--- a/data/raw/문제_SERVICE.xlsx
+++ b/data/raw/문제_SERVICE.xlsx
@@ -739,10 +739,14 @@
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -814,10 +818,14 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -889,10 +897,14 @@
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -964,10 +976,14 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1039,10 +1055,14 @@
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1114,10 +1134,14 @@
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1189,10 +1213,14 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1264,10 +1292,14 @@
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1339,10 +1371,14 @@
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1414,10 +1450,14 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1489,10 +1529,14 @@
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1564,10 +1608,14 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 법령 원문 미확인(작성자 지식) – 원문 대조 필수</t>
@@ -1639,10 +1687,14 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1714,10 +1766,14 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1789,10 +1845,14 @@
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1864,10 +1924,14 @@
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1939,10 +2003,14 @@
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2014,10 +2082,14 @@
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2089,10 +2161,14 @@
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2164,10 +2240,14 @@
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2239,10 +2319,14 @@
       <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2314,10 +2398,14 @@
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2389,10 +2477,14 @@
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2464,10 +2556,14 @@
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2539,10 +2635,14 @@
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2614,10 +2714,14 @@
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2689,10 +2793,14 @@
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2764,10 +2872,14 @@
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2839,10 +2951,14 @@
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2914,10 +3030,14 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 고객서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2989,10 +3109,14 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -3064,10 +3188,14 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3139,10 +3267,14 @@
       <c r="N34" s="3" t="n"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -3214,10 +3346,14 @@
       <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -3289,10 +3425,14 @@
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3364,10 +3504,14 @@
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -3439,10 +3583,14 @@
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -3514,10 +3662,14 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3589,10 +3741,14 @@
       <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3664,10 +3820,14 @@
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -3739,10 +3899,14 @@
       <c r="N42" s="3" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3814,10 +3978,14 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3889,10 +4057,14 @@
       <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3964,10 +4136,14 @@
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4039,10 +4215,14 @@
       <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4114,10 +4294,14 @@
       <c r="N47" s="3" t="n"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4189,10 +4373,14 @@
       <c r="N48" s="3" t="n"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -4264,10 +4452,14 @@
       <c r="N49" s="3" t="n"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4339,10 +4531,14 @@
       <c r="N50" s="3" t="n"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4414,10 +4610,14 @@
       <c r="N51" s="3" t="n"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4489,10 +4689,14 @@
       <c r="N52" s="3" t="n"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4564,10 +4768,14 @@
       <c r="N53" s="3" t="n"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4639,10 +4847,14 @@
       <c r="N54" s="3" t="n"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4714,10 +4926,14 @@
       <c r="N55" s="3" t="n"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4789,10 +5005,14 @@
       <c r="N56" s="3" t="n"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -4864,10 +5084,14 @@
       <c r="N57" s="3" t="n"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4939,10 +5163,14 @@
       <c r="N58" s="3" t="n"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5014,10 +5242,14 @@
       <c r="N59" s="3" t="n"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5089,10 +5321,14 @@
       <c r="N60" s="3" t="n"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5164,10 +5400,14 @@
       <c r="N61" s="3" t="n"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5239,10 +5479,14 @@
       <c r="N62" s="3" t="n"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5314,10 +5558,14 @@
       <c r="N63" s="3" t="n"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5389,10 +5637,14 @@
       <c r="N64" s="3" t="n"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5464,10 +5716,14 @@
       <c r="N65" s="3" t="n"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5539,10 +5795,14 @@
       <c r="N66" s="3" t="n"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5614,10 +5874,14 @@
       <c r="N67" s="3" t="n"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5689,10 +5953,14 @@
       <c r="N68" s="3" t="n"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5764,10 +6032,14 @@
       <c r="N69" s="3" t="n"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5839,10 +6111,14 @@
       <c r="N70" s="3" t="n"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -5914,10 +6190,14 @@
       <c r="N71" s="3" t="n"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -5989,10 +6269,14 @@
       <c r="N72" s="3" t="n"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -6064,10 +6348,14 @@
       <c r="N73" s="3" t="n"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -6139,10 +6427,14 @@
       <c r="N74" s="3" t="n"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -6214,10 +6506,14 @@
       <c r="N75" s="3" t="n"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(용어·수치 포함) – 공단 교재·KS 기준과 대조 필수</t>
@@ -6289,10 +6585,14 @@
       <c r="N76" s="3" t="n"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 서비스·물류 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>

--- a/data/raw/문제_SERVICE.xlsx
+++ b/data/raw/문제_SERVICE.xlsx
@@ -6600,1429 +6600,5629 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="n"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>직업이 가지는 의미 가운데 '일을 통해 수입을 얻어 생활을 유지한다'는 것에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>사회적 의미</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>경제적 의미</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>철학적 의미</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>정신적 의미</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>일하여 소득을 얻고 생계를 꾸리는 측면은 직업의 경제적 의미이다.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>돈과 생활비를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P77" s="3" t="n"/>
-      <c r="Q77" s="3" t="n"/>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 직업의 의미</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="3" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>자기 일을 하늘이 맡긴 일로 여기고 그 일에 긍지와 애정을 가지는 바람직한 직업관은?</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>전문의식</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>봉사정신</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>천직의식</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>직분의식</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>자신의 일을 하늘이 내려 준 일로 생각하고 즐겁게 몰두하는 태도를 천직의식이라 한다.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>자기 일을 운명처럼 받아들이고 사랑하는 태도입니다. 맡은 '몫'을 다하는 태도와는 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P78" s="3" t="n"/>
-      <c r="Q78" s="3" t="n"/>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 바람직한 직업관</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="n"/>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="n"/>
-      <c r="L79" s="3" t="n"/>
-      <c r="M79" s="3" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>다음 중 잘못된 직업관에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>맡은 일에 끝까지 책임을 지려는 책임의식</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>다른 사람과 사회를 위해 일하려는 봉사정신</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>능력보다 출신·배경을 더 중요하게 여기는 귀속적 직업관</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>자기 일에 전문 지식과 기술을 갖추려는 전문의식</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>타고난 신분이나 배경을 능력보다 중시하는 귀속적 직업관은 잘못된 직업관이다. 나머지는 바람직한 직업관이다.</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>본인의 노력과 상관없이 정해지는 것을 중시하는 태도를 찾으세요.</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N79" s="3" t="n"/>
-      <c r="O79" s="3" t="n"/>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P79" s="3" t="n"/>
-      <c r="Q79" s="3" t="n"/>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 잘못된 직업관</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="3" t="n"/>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="n"/>
-      <c r="L80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자의 기본자세 중 '추측 운전을 하지 않는다'의 뜻으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>다른 운전자의 신호를 무시하고 내 판단대로 간다</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>날씨 예보를 보지 않고 운행한다</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>내비게이션의 도착 예정 시간을 믿지 않는다</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>상대가 당연히 양보하거나 멈출 것이라고 내 마음대로 판단하지 않는다</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>'저 차가 서겠지' 같은 자기 중심적 예측은 사고로 이어지므로 상대의 행동을 확인하며 운전해야 한다.</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>'~하겠지' 운전과 반대되는 태도를 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P80" s="3" t="n"/>
-      <c r="Q80" s="3" t="n"/>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="n"/>
-      <c r="L81" s="3" t="n"/>
-      <c r="M81" s="3" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자의 기본자세로 바람직하지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>교통법규를 이해하고 지킨다</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>여유를 가지고 양보 운전을 한다</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>오랜 경력을 믿고 운전 기술을 과신한다</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>운전 중에는 휴대전화 등에 신경 쓰지 않고 운전에만 집중한다</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>경력이 길수록 자신의 기술을 과신하기 쉬운데, 이는 방심과 무리한 운전을 낳아 사고 원인이 된다.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>자신감이 지나치면 어떤 일이 생기는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P81" s="3" t="n"/>
-      <c r="Q81" s="3" t="n"/>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="3" t="n"/>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" s="3" t="n"/>
-      <c r="J82" s="3" t="n"/>
-      <c r="K82" s="3" t="n"/>
-      <c r="L82" s="3" t="n"/>
-      <c r="M82" s="3" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자의 심신 상태 관리로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>개인적인 고민은 운행 중 잠시 내려놓고 운전에 집중한다</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>화가 난 상태에서는 운전으로 기분을 풀기 위해 속도를 낸다</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>운행 전 충분히 쉬어 피로를 풀어 둔다</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>몸이 아프면 무리하지 말고 회사에 알린다</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>감정이 흥분된 상태의 운전은 공격적 운전과 판단 착오로 이어지므로, 마음을 안정시킨 뒤 운전해야 한다.</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>감정과 가속 페달이 연결되면 어떤 결과가 생길까요?</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N82" s="3" t="n"/>
-      <c r="O82" s="3" t="n"/>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P82" s="3" t="n"/>
-      <c r="Q82" s="3" t="n"/>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 심신상태의 안정</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>서비스의 특징 중 '서비스는 만드는 것과 쓰는 것이 같은 순간에 일어난다'는 성질은?</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>무소유권</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>동시성</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>무형성</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>소멸성</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>운송서비스처럼 서비스는 제공되는 순간 고객이 바로 소비하므로 생산과 소비가 분리되지 않는다.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>시간의 '같음'에 주목하세요.</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P83" s="3" t="n"/>
-      <c r="Q83" s="3" t="n"/>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스의 특징 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="3" t="n"/>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" s="3" t="n"/>
-      <c r="J84" s="3" t="n"/>
-      <c r="K84" s="3" t="n"/>
-      <c r="L84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>운송 서비스를 이용한 고객이 서비스를 받은 뒤에도 그 서비스 자체를 가질 수는 없다는 서비스의 특징은?</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>인적 의존성</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>동시성</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>무형성</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>무소유권</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>서비스는 이용할 권리는 있어도 물건처럼 소유권이 넘어가지 않는다는 점에서 무소유권의 특징이 있다.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>'가진다'는 개념이 성립하지 않는 성질입니다.</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P84" s="3" t="n"/>
-      <c r="Q84" s="3" t="n"/>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스의 특징</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
-      <c r="I85" s="3" t="n"/>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="n"/>
-      <c r="L85" s="3" t="n"/>
-      <c r="M85" s="3" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>서비스는 눈에 보이지 않아 구매 전에 직접 만지거나 확인하기 어렵다는 특징은?</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>무형성</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>이질성</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>소멸성</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>동시성</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>서비스는 형태가 없는 행위이므로 품질을 미리 보고 판단하기 어렵다. 이를 무형성이라 한다.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>운송 서비스를 미리 손에 들고 살펴볼 수 있는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P85" s="3" t="n"/>
-      <c r="Q85" s="3" t="n"/>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스의 특징</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="n"/>
-      <c r="L86" s="3" t="n"/>
-      <c r="M86" s="3" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>단골 고객의 이름과 지난번 요청 사항을 기억해 먼저 인사하는 것은 고객의 어떤 욕구를 채워 주는가?</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>기억되고 싶은 욕구</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>할인받고 싶은 욕구</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>혼자 있고 싶은 욕구</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>빨리 떠나고 싶은 욕구</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>고객은 자신을 알아보고 기억해 주기를 바라므로, 이름과 요청을 기억해 주면 만족도가 높아진다.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>'나를 알아봐 주는 것'이 주는 기분을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P86" s="3" t="n"/>
-      <c r="Q86" s="3" t="n"/>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객의 욕구</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="n"/>
-      <c r="L87" s="3" t="n"/>
-      <c r="M87" s="3" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>고객이 거래를 그만두는 이유 가운데 일반적으로 가장 큰 비중을 차지하는 것은?</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>제품 가격</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>이사 등 환경 변화</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>종업원의 불친절</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>경쟁사의 광고</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>고객 이탈 원인 조사에서 가장 큰 비중을 차지하는 것은 직원의 불친절한 태도이다.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>가격이나 품질보다 '사람'과 관련된 요인을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N87" s="3" t="n"/>
-      <c r="O87" s="3" t="n"/>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P87" s="3" t="n"/>
-      <c r="Q87" s="3" t="n"/>
+      <c r="Q87" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객이 거래를 중단하는 이유</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="n"/>
-      <c r="L88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>신규 고객을 확보하는 것과 기존 고객을 유지하는 것에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>기존 고객을 지키는 비용이 훨씬 크다</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>기존 고객은 관리하지 않아도 저절로 유지된다</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>두 비용은 항상 같다</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>새 고객을 얻는 데 드는 비용이 기존 고객을 지키는 비용보다 훨씬 크다</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>새 고객을 끌어오는 데는 기존 고객 유지보다 몇 배의 비용이 들어서, 기존 고객의 만족 관리가 중요하다.</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>광고·영업에 드는 노력을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P88" s="3" t="n"/>
-      <c r="Q88" s="3" t="n"/>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객만족의 중요성</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="n"/>
-      <c r="L89" s="3" t="n"/>
-      <c r="M89" s="3" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>고객만족의 품질 요소 중 고객이 상품을 구매하기까지 고객과 만나는 접점에서 이루어지는 영업 활동의 품질을 무엇이라 하는가?</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>영업품질</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>상품품질</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>설계품질</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>서비스품질</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>상품품질은 하드웨어, 서비스품질은 휴먼웨어에 해당하며, 고객 접점에서 상품을 판매하기까지의 활동 품질은 영업품질이다.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>판매에 이르는 과정의 활동을 뜻하는 말입니다.</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P89" s="3" t="n"/>
-      <c r="Q89" s="3" t="n"/>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객만족을 위한 3가지 품질</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="n"/>
-      <c r="L90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>고객만족의 3가지 품질 요소 가운데 '휴먼웨어(Humanware) 품질'이라고 부르는 것은?</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>영업품질</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>포장품질</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>서비스품질</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>상품품질</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>직원의 친절·태도처럼 사람이 제공하는 품질은 서비스품질이며 휴먼웨어 품질이라고 한다.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>직원의 친절·태도처럼 사람이 직접 만들어 내는 품질을 가리킵니다.</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
+      <c r="O90" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P90" s="3" t="n"/>
-      <c r="Q90" s="3" t="n"/>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객만족을 위한 3가지 품질</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n"/>
-      <c r="G91" s="3" t="n"/>
-      <c r="H91" s="3" t="n"/>
-      <c r="I91" s="3" t="n"/>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="n"/>
-      <c r="L91" s="3" t="n"/>
-      <c r="M91" s="3" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>고객의 요청에 기꺼이, 그리고 빠르게 도움을 주려는 의지를 뜻하는 서비스 품질 요소는?</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>확신성</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>응답성</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>유형성</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>고객의 요구에 즉시 반응하고 신속하게 서비스를 제공하려는 자세를 응답성(신속한 대응)이라 한다.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>'반응하는 속도'와 관련된 요소입니다.</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N91" s="3" t="n"/>
-      <c r="O91" s="3" t="n"/>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P91" s="3" t="n"/>
-      <c r="Q91" s="3" t="n"/>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스 품질의 평가 기준 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="n"/>
-      <c r="L92" s="3" t="n"/>
-      <c r="M92" s="3" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>고객 한 사람 한 사람에게 관심을 기울이고 고객 입장에서 이해하려는 서비스 품질 요소는?</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>유형성</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>공감성</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>응답성</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>고객을 개별적으로 배려하고 입장을 이해하려는 노력은 공감성에 해당한다.</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>고객의 마음을 내 일처럼 느끼려는 노력과 관련됩니다.</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N92" s="3" t="n"/>
-      <c r="O92" s="3" t="n"/>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P92" s="3" t="n"/>
-      <c r="Q92" s="3" t="n"/>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: SERVQUAL 5차원(유형성·신뢰성·응답성·확신성·공감성) 일반 서비스 이론</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>불만 고객 응대 기법 중 처리하는 사람, 시간, 장소를 바꾸어 고객의 감정을 가라앉히는 방법은?</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>5S 기법</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>MTP 기법</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ABC 분석</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>SWOT 분석</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>MTP는 사람(Man)·시간(Time)·장소(Place)를 바꾸어 흥분한 고객을 진정시키는 불만 처리 기법이다.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>흥분한 고객 앞의 상황 요소들을 하나씩 바꾸어 분위기를 전환하는 기법입니다.</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N93" s="3" t="n"/>
-      <c r="O93" s="3" t="n"/>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P93" s="3" t="n"/>
-      <c r="Q93" s="3" t="n"/>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 일반 고객서비스(CS) 이론 – 불만 고객 응대 기법</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="3" t="n"/>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
-      <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="n"/>
-      <c r="L94" s="3" t="n"/>
-      <c r="M94" s="3" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>배송 지연으로 항의하는 고객에게 하는 말로 가장 바람직한 것은?</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>불편을 드려 죄송합니다. 지금 위치를 확인해 언제쯤 도착할지 바로 알려 드리겠습니다</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>원래 요즘은 다 늦습니다</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>그건 회사에 직접 따지세요</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>제 잘못이 아니라 터미널에서 늦게 내려온 겁니다</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>불만 처리에서는 변명이나 책임 전가 없이 먼저 사과하고, 구체적인 해결 방법과 시간을 안내해야 한다.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>변명과 해결책 중 고객이 원하는 것이 무엇일지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N94" s="3" t="n"/>
-      <c r="O94" s="3" t="n"/>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P94" s="3" t="n"/>
-      <c r="Q94" s="3" t="n"/>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객 불만 처리 요령</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="3" t="n"/>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n"/>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="3" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="n"/>
-      <c r="L95" s="3" t="n"/>
-      <c r="M95" s="3" t="n"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>운송 서비스에서 '외부 고객'에 해당하지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>화물을 받는 수하인</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>같은 회사의 배차 담당 직원</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>화물을 맡기는 화주</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>택배를 보내려는 개인 소비자</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>같은 회사 직원은 내부 고객이며, 화주·수하인·이용자는 외부 고객이다.</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>회사 울타리 안과 밖을 구분해 보세요.</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N95" s="3" t="n"/>
-      <c r="O95" s="3" t="n"/>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P95" s="3" t="n"/>
-      <c r="Q95" s="3" t="n"/>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객의 개념</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="3" t="n"/>
-      <c r="L96" s="3" t="n"/>
-      <c r="M96" s="3" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>일상에서 고객이나 윗사람에게 하는 보통 인사(보통례)의 일반적인 허리 굽힘 각도는?</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>약 60도</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>약 5도</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>약 90도</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>약 30도</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>인사는 가벼운 인사 약 15도, 보통 인사 약 30도, 정중한 인사 약 45도가 기준이다.</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>가벼운 인사와 정중한 인사의 중간 정도입니다.</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N96" s="3" t="n"/>
-      <c r="O96" s="3" t="n"/>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P96" s="3" t="n"/>
-      <c r="Q96" s="3" t="n"/>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 인사의 종류</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n"/>
-      <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="3" t="n"/>
-      <c r="L97" s="3" t="n"/>
-      <c r="M97" s="3" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>고객을 대할 때 바람직한 시선 처리로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>고객의 말이 끝날 때까지 다른 곳을 본다</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>부드러운 눈길로 고객의 눈높이에 맞추어 바라본다</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>곁눈질로 슬쩍 본다</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>위아래로 훑어보며 상대를 살핀다</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>훑어보기·곁눈질·딴 데 보기는 불쾌감을 주므로 자연스럽게 눈높이를 맞추어 바라보는 것이 좋다.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>내가 고객이라면 어떤 눈길이 편안할지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N97" s="3" t="n"/>
-      <c r="O97" s="3" t="n"/>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P97" s="3" t="n"/>
-      <c r="Q97" s="3" t="n"/>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 표정과 시선</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="3" t="n"/>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n"/>
-      <c r="G98" s="3" t="n"/>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="n"/>
-      <c r="K98" s="3" t="n"/>
-      <c r="L98" s="3" t="n"/>
-      <c r="M98" s="3" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자 복장의 기본 원칙으로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>개성을 드러내도록 화려하게 입는다</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>회사 규정에 맞게 통일감 있게 입는다</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>계절과 작업에 맞게 활동하기 편하게 입는다</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>깨끗하고 단정하게 입는다</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>복장은 청결·단정·품위·규정 준수가 원칙이며, 지나치게 화려한 차림은 고객에게 신뢰감을 주지 못한다.</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>고객이 운전자를 볼 때 원하는 느낌은 '튀는 것'일까요, '믿음직한 것'일까요?</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N98" s="3" t="n"/>
-      <c r="O98" s="3" t="n"/>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P98" s="3" t="n"/>
-      <c r="Q98" s="3" t="n"/>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 복장과 용모</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n"/>
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="3" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="n"/>
-      <c r="K99" s="3" t="n"/>
-      <c r="L99" s="3" t="n"/>
-      <c r="M99" s="3" t="n"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>회사로 걸려 온 고객 전화를 받을 때 가장 먼저 해야 할 것으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>잠시 기다리라고 하고 다른 일을 마친다</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>인사와 함께 회사명(소속)과 이름을 밝힌다</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>누구냐고 먼저 묻는다</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>용건을 말할 때까지 아무 말도 하지 않는다</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>전화를 받으면 먼저 인사와 함께 소속과 이름을 밝혀 고객이 제대로 연결되었는지 알 수 있게 한다.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>고객이 '제대로 걸었나?' 하고 궁금해하지 않게 하려면 무엇을 알려야 할까요?</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N99" s="3" t="n"/>
-      <c r="O99" s="3" t="n"/>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P99" s="3" t="n"/>
-      <c r="Q99" s="3" t="n"/>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 전화 응대</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="3" t="n"/>
-      <c r="C100" s="3" t="n"/>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n"/>
-      <c r="G100" s="3" t="n"/>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="3" t="n"/>
-      <c r="J100" s="3" t="n"/>
-      <c r="K100" s="3" t="n"/>
-      <c r="L100" s="3" t="n"/>
-      <c r="M100" s="3" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>화물을 적재할 때 운전자 수칙으로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>화물을 한쪽으로 치우치지 않게 고르게 싣는다</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>운행 횟수를 줄이기 위해 최대적재량보다 더 싣는다</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>화물이 떨어지지 않도록 덮개를 씌우고 단단히 묶는다</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>출발 전 적재 상태를 다시 확인한다</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>과적은 제동거리 증가·차량 고장·도로 파손을 일으키므로 금지된다.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>차량에는 정해진 한계가 있습니다.</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N100" s="3" t="n"/>
-      <c r="O100" s="3" t="n"/>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P100" s="3" t="n"/>
-      <c r="Q100" s="3" t="n"/>
+      <c r="Q100" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운전자 수칙 – 화물 적재</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="3" t="n"/>
-      <c r="C101" s="3" t="n"/>
-      <c r="D101" s="3" t="n"/>
-      <c r="E101" s="3" t="n"/>
-      <c r="F101" s="3" t="n"/>
-      <c r="G101" s="3" t="n"/>
-      <c r="H101" s="3" t="n"/>
-      <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="n"/>
-      <c r="K101" s="3" t="n"/>
-      <c r="L101" s="3" t="n"/>
-      <c r="M101" s="3" t="n"/>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>운행 중 운전자 수칙으로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>신호가 바뀌자마자 급출발하여 먼저 교차로를 빠져나간다</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>보행자가 있는 곳에서는 서행한다</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>앞차와 충분한 안전거리를 둔다</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>차로 변경 전에는 방향지시등으로 미리 알린다</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>신호 변경 직후 급출발은 신호를 늦게 통과하는 차량·보행자와 충돌할 위험이 크다.</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>신호가 막 바뀐 교차로에 아직 남아 있을 수 있는 것을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N101" s="3" t="n"/>
-      <c r="O101" s="3" t="n"/>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P101" s="3" t="n"/>
-      <c r="Q101" s="3" t="n"/>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운전자 수칙 – 운행 중 준수사항</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="3" t="n"/>
-      <c r="G102" s="3" t="n"/>
-      <c r="H102" s="3" t="n"/>
-      <c r="I102" s="3" t="n"/>
-      <c r="J102" s="3" t="n"/>
-      <c r="K102" s="3" t="n"/>
-      <c r="L102" s="3" t="n"/>
-      <c r="M102" s="3" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>'로지스틱스(Logistics)'라는 말은 원래 어느 분야에서 쓰이던 용어에서 비롯되었는가?</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>군사 분야의 병참</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>의료 분야의 처방</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>건설 분야의 설계</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>농업 분야의 수확</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>로지스틱스는 군대의 물자 보급·수송을 뜻하는 병참에서 유래하여 기업 물류 관리로 확대된 개념이다.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>전쟁터에서 무기와 식량을 제때 보급하는 일을 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N102" s="3" t="n"/>
-      <c r="O102" s="3" t="n"/>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P102" s="3" t="n"/>
-      <c r="Q102" s="3" t="n"/>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 로지스틱스</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="3" t="n"/>
-      <c r="D103" s="3" t="n"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="3" t="n"/>
-      <c r="H103" s="3" t="n"/>
-      <c r="I103" s="3" t="n"/>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="3" t="n"/>
-      <c r="L103" s="3" t="n"/>
-      <c r="M103" s="3" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>물류 관리 개념이 발전해 온 순서로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>로지스틱스 → 공급망관리(SCM) → 물적유통(PD)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>물적유통(PD) → 로지스틱스 → 공급망관리(SCM)</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>공급망관리(SCM) → 로지스틱스 → 물적유통(PD)</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>물적유통(PD) → 공급망관리(SCM) → 로지스틱스</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>단순 판매물류 중심의 물적유통에서 기업 전체를 통합한 로지스틱스로, 다시 기업 간 연결인 SCM으로 넓어졌다.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>관리 범위가 '한 기능 → 한 기업 → 여러 기업'으로 넓어지는 흐름입니다.</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N103" s="3" t="n"/>
-      <c r="O103" s="3" t="n"/>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P103" s="3" t="n"/>
-      <c r="Q103" s="3" t="n"/>
+      <c r="Q103" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류 개념의 변천</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="3" t="n"/>
-      <c r="C104" s="3" t="n"/>
-      <c r="D104" s="3" t="n"/>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="3" t="n"/>
-      <c r="G104" s="3" t="n"/>
-      <c r="H104" s="3" t="n"/>
-      <c r="I104" s="3" t="n"/>
-      <c r="J104" s="3" t="n"/>
-      <c r="K104" s="3" t="n"/>
-      <c r="L104" s="3" t="n"/>
-      <c r="M104" s="3" t="n"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>국민경제 측면에서 물류가 하는 역할로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>물가 상승을 억제하는 데 도움을 준다</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>특정 기업의 독점 이익을 늘린다</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>지역 간 균형 있는 발전에 이바지한다</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>사회간접자본의 효율을 높인다</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>효율적인 물류는 물가 안정, 지역 균형 발전, 사회간접자본 활용 등 국민경제 전체에 기여한다.</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>'국민경제'라는 말의 범위를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N104" s="3" t="n"/>
-      <c r="O104" s="3" t="n"/>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P104" s="3" t="n"/>
-      <c r="Q104" s="3" t="n"/>
+      <c r="Q104" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류의 역할</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n"/>
-      <c r="B105" s="3" t="n"/>
-      <c r="C105" s="3" t="n"/>
-      <c r="D105" s="3" t="n"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="3" t="n"/>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="n"/>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="3" t="n"/>
-      <c r="L105" s="3" t="n"/>
-      <c r="M105" s="3" t="n"/>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>기업이 매출 증대, 제조원가 절감에 이어 물류비 절감을 새로운 이익 원천으로 보는 말은?</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>규모의 경제</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>블루오션</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>제2의 시장</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>제3의 이익원</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>물류비 절감은 매출 증대와 생산원가 절감 다음의 세 번째 이익 원천이라는 뜻에서 '제3의 이익원'이라 한다.</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>물류비 절감이 기업 이익을 늘리는 또 하나의 원천이라는 뜻입니다.</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N105" s="3" t="n"/>
-      <c r="O105" s="3" t="n"/>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P105" s="3" t="n"/>
-      <c r="Q105" s="3" t="n"/>
+      <c r="Q105" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류의 중요성 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="3" t="n"/>
-      <c r="C106" s="3" t="n"/>
-      <c r="D106" s="3" t="n"/>
-      <c r="E106" s="3" t="n"/>
-      <c r="F106" s="3" t="n"/>
-      <c r="G106" s="3" t="n"/>
-      <c r="H106" s="3" t="n"/>
-      <c r="I106" s="3" t="n"/>
-      <c r="J106" s="3" t="n"/>
-      <c r="K106" s="3" t="n"/>
-      <c r="L106" s="3" t="n"/>
-      <c r="M106" s="3" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>물류 관리에서 '상충관계(Trade-off)'의 예로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>서비스 수준을 높이면 물류비는 반드시 줄어든다</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>물류 기능들은 서로 아무 영향을 주지 않는다</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>재고를 줄이면 보관비는 줄지만 배송 횟수가 늘어 운송비가 늘 수 있다</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>운송비와 보관비는 항상 함께 줄어든다</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>물류 기능 사이에는 한쪽 비용을 줄이면 다른 쪽 비용이 늘어나는 상충관계가 있어 전체 최적화가 필요하다.</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>한쪽을 누르면 다른 쪽이 올라가는 시소를 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N106" s="3" t="n"/>
-      <c r="O106" s="3" t="n"/>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P106" s="3" t="n"/>
-      <c r="Q106" s="3" t="n"/>
+      <c r="Q106" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류관리의 목표</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="3" t="n"/>
-      <c r="C107" s="3" t="n"/>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="3" t="n"/>
-      <c r="H107" s="3" t="n"/>
-      <c r="I107" s="3" t="n"/>
-      <c r="J107" s="3" t="n"/>
-      <c r="K107" s="3" t="n"/>
-      <c r="L107" s="3" t="n"/>
-      <c r="M107" s="3" t="n"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>원자재나 부품을 공급자로부터 사들여 생산 공정에 투입되기 전까지의 물류는?</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>생산물류</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>판매물류</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>폐기물류</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>조달물류</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>원재료·부품의 구매부터 제조업체 창고 입고·생산 투입 전까지를 조달물류라 한다.</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>물류를 영역별로 나눌 때 생산에 들어가기 '전' 단계입니다.</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N107" s="3" t="n"/>
-      <c r="O107" s="3" t="n"/>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P107" s="3" t="n"/>
-      <c r="Q107" s="3" t="n"/>
+      <c r="Q107" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류의 영역 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="3" t="n"/>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
-      <c r="G108" s="3" t="n"/>
-      <c r="H108" s="3" t="n"/>
-      <c r="I108" s="3" t="n"/>
-      <c r="J108" s="3" t="n"/>
-      <c r="K108" s="3" t="n"/>
-      <c r="L108" s="3" t="n"/>
-      <c r="M108" s="3" t="n"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>'수송'과 '배송'의 구분으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>수송은 단거리 소량, 배송은 장거리 대량 이동이다</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>수송은 거점 간 장거리 대량 이동, 배송은 거점에서 고객까지 단거리 소량 이동이다</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>수송은 항공만, 배송은 철도만을 뜻한다</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>두 말은 완전히 같은 뜻이다</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>공장·물류센터 사이처럼 거점 간 대량 이동은 수송, 물류센터에서 고객에게 나누어 보내는 것은 배송이다.</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>택배 기사의 마지막 구간 업무가 어느 쪽인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N108" s="3" t="n"/>
-      <c r="O108" s="3" t="n"/>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P108" s="3" t="n"/>
-      <c r="Q108" s="3" t="n"/>
+      <c r="Q108" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 운송 관련 용어</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="3" t="n"/>
-      <c r="C109" s="3" t="n"/>
-      <c r="D109" s="3" t="n"/>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="3" t="n"/>
-      <c r="G109" s="3" t="n"/>
-      <c r="H109" s="3" t="n"/>
-      <c r="I109" s="3" t="n"/>
-      <c r="J109" s="3" t="n"/>
-      <c r="K109" s="3" t="n"/>
-      <c r="L109" s="3" t="n"/>
-      <c r="M109" s="3" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>고객이 주문한 시점부터 물품을 받을 때까지 걸리는 시간을 무엇이라 하는가?</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>대기시간</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>택트타임</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>공차시간</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>리드타임</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>주문에서 납품까지 걸리는 시간을 리드타임이라 하며, 짧을수록 고객 서비스 수준이 높다.</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>주문과 도착 사이의 '간격'을 가리키는 용어입니다.</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N109" s="3" t="n"/>
-      <c r="O109" s="3" t="n"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P109" s="3" t="n"/>
-      <c r="Q109" s="3" t="n"/>
+      <c r="Q109" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 일반 이론 – 리드타임</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="3" t="n"/>
-      <c r="C110" s="3" t="n"/>
-      <c r="D110" s="3" t="n"/>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n"/>
-      <c r="G110" s="3" t="n"/>
-      <c r="H110" s="3" t="n"/>
-      <c r="I110" s="3" t="n"/>
-      <c r="J110" s="3" t="n"/>
-      <c r="K110" s="3" t="n"/>
-      <c r="L110" s="3" t="n"/>
-      <c r="M110" s="3" t="n"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>화주 기업이 별도로 세운 물류 자회사에 물류 업무를 맡기는 형태는?</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>제3자 물류</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>제2자 물류</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>제1자 물류</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>제4자 물류</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>기업이 직접 하면 제1자, 물류 자회사가 하면 제2자, 독립된 외부 전문업체에 맡기면 제3자 물류이다.</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>자기 회사와 완전히 독립된 업체인지, 같은 그룹 회사인지 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N110" s="3" t="n"/>
-      <c r="O110" s="3" t="n"/>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P110" s="3" t="n"/>
-      <c r="Q110" s="3" t="n"/>
+      <c r="Q110" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 제3자 물류</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="3" t="n"/>
-      <c r="C111" s="3" t="n"/>
-      <c r="D111" s="3" t="n"/>
-      <c r="E111" s="3" t="n"/>
-      <c r="F111" s="3" t="n"/>
-      <c r="G111" s="3" t="n"/>
-      <c r="H111" s="3" t="n"/>
-      <c r="I111" s="3" t="n"/>
-      <c r="J111" s="3" t="n"/>
-      <c r="K111" s="3" t="n"/>
-      <c r="L111" s="3" t="n"/>
-      <c r="M111" s="3" t="n"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0110</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>화주 기업이 제3자 물류를 이용할 때 기대할 수 있는 효과로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>물류 시설·인력에 대한 고정 투자가 크게 늘어난다</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>핵심 사업에 경영 자원을 집중할 수 있다</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>전문 업체의 노하우로 물류 효율이 높아진다</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>물류비를 절감할 수 있다</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>제3자 물류는 물류 시설 투자를 외부에 맡겨 고정비 부담을 줄이고 핵심 역량에 집중하게 한다.</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>외부에 맡기면 내 자산은 늘어날까요, 줄어들까요?</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N111" s="3" t="n"/>
-      <c r="O111" s="3" t="n"/>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P111" s="3" t="n"/>
-      <c r="Q111" s="3" t="n"/>
+      <c r="Q111" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 제3자 물류 기대효과</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n"/>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
-      <c r="J112" s="3" t="n"/>
-      <c r="K112" s="3" t="n"/>
-      <c r="L112" s="3" t="n"/>
-      <c r="M112" s="3" t="n"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0111</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>제4자 물류(4PL)의 단계에 해당하지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>실행(Execution)</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>전환(Transformation)</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>독점(Monopoly)</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>재창조(Reinvention)</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>4PL은 재창조, 전환, 이행, 실행의 4단계로 설명되며 독점은 해당하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>공급망을 새로 짜고 바꾸고 실천하는 흐름에 맞지 않는 단어를 고르세요.</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N112" s="3" t="n"/>
-      <c r="O112" s="3" t="n"/>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P112" s="3" t="n"/>
-      <c r="Q112" s="3" t="n"/>
+      <c r="Q112" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 제4자 물류 4단계</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n"/>
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="3" t="n"/>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="3" t="n"/>
-      <c r="L113" s="3" t="n"/>
-      <c r="M113" s="3" t="n"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0112</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>기존의 기업 단위 물류 관리와 비교한 공급망관리(SCM)의 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>재고는 많을수록 좋다고 본다</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>자기 회사의 이익만 최대화하는 것이 목표이다</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>공급망에 참여하는 여러 기업이 정보를 공유하고 협력하여 전체 최적화를 추구한다</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>협력 업체와 정보를 공유하지 않는다</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>SCM은 공급자부터 소비자까지 여러 기업이 정보를 공유하며 협력해 공급망 전체의 효율을 높이는 것이다.</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>'망(網)'이라는 글자가 뜻하는 범위를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N113" s="3" t="n"/>
-      <c r="O113" s="3" t="n"/>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P113" s="3" t="n"/>
-      <c r="Q113" s="3" t="n"/>
+      <c r="Q113" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 공급망관리</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n"/>
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="3" t="n"/>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n"/>
-      <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="n"/>
-      <c r="I114" s="3" t="n"/>
-      <c r="J114" s="3" t="n"/>
-      <c r="K114" s="3" t="n"/>
-      <c r="L114" s="3" t="n"/>
-      <c r="M114" s="3" t="n"/>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0113</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>의류·섬유 산업에서 시작된 것으로, 생산·유통 업체가 판매 정보를 공유해 소비자 요구에 빠르게 대응하는 기법은?</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>ECR</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>CALS</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>QR은 미국 섬유·의류 업계에서 시작된 SCM 기법으로 판매 정보 공유를 통해 빠르게 보충·생산한다.</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>속도를 강조하는 기법으로, 패션처럼 유행이 빨리 바뀌는 업종에서 출발했습니다.</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N114" s="3" t="n"/>
-      <c r="O114" s="3" t="n"/>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P114" s="3" t="n"/>
-      <c r="Q114" s="3" t="n"/>
+      <c r="Q114" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – SCM 주요 기법 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="n"/>
-      <c r="H115" s="3" t="n"/>
-      <c r="I115" s="3" t="n"/>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="n"/>
-      <c r="L115" s="3" t="n"/>
-      <c r="M115" s="3" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0114</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>식품·잡화 업계에서 시작된 것으로, 제조업체와 유통업체가 협력하여 소비자에게 더 큰 가치를 효율적으로 제공하려는 SCM 기법은?</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>JIT</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>ECR</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>ECR(효율적 소비자 대응)은 미국 식품·잡화 업계에서 시작되어 공급망 전체의 비효율을 줄이려는 전략이다.</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>슈퍼마켓 상품처럼 소비자 가까이에서 시작된 기법으로, 다른 보기는 생산·자원 관리나 적시 공급 개념입니다.</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N115" s="3" t="n"/>
-      <c r="O115" s="3" t="n"/>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P115" s="3" t="n"/>
-      <c r="Q115" s="3" t="n"/>
+      <c r="Q115" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – SCM 주요 기법</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="3" t="n"/>
-      <c r="C116" s="3" t="n"/>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="n"/>
-      <c r="I116" s="3" t="n"/>
-      <c r="J116" s="3" t="n"/>
-      <c r="K116" s="3" t="n"/>
-      <c r="L116" s="3" t="n"/>
-      <c r="M116" s="3" t="n"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0115</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>공급자가 판매처의 재고 정보를 받아 판매처의 재고를 직접 관리하고 보충하는 방식은?</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>CALS</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>VMI</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>VMI는 공급자(Vendor)가 고객의 재고 수준을 보고 주문 없이도 필요한 만큼 보충하는 방식이다.</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>재고 관리의 주체가 '물건을 파는 쪽'으로 바뀝니다.</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N116" s="3" t="n"/>
-      <c r="O116" s="3" t="n"/>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P116" s="3" t="n"/>
-      <c r="Q116" s="3" t="n"/>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: SCM 일반 이론 – VMI · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
-      <c r="G117" s="3" t="n"/>
-      <c r="H117" s="3" t="n"/>
-      <c r="I117" s="3" t="n"/>
-      <c r="J117" s="3" t="n"/>
-      <c r="K117" s="3" t="n"/>
-      <c r="L117" s="3" t="n"/>
-      <c r="M117" s="3" t="n"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0116</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>기업의 생산·재무·인사·물류 등 모든 경영 자원을 하나의 통합 시스템으로 관리하는 것은?</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>RFID</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>ERP는 기업 전체의 자원을 통합 관리하여 업무 효율을 높이는 정보 시스템이다.</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>부서별로 흩어진 시스템을 회사 전체 하나로 묶는다는 점에 주목하세요.</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N117" s="3" t="n"/>
-      <c r="O117" s="3" t="n"/>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P117" s="3" t="n"/>
-      <c r="Q117" s="3" t="n"/>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류 정보 시스템 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n"/>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="n"/>
-      <c r="L118" s="3" t="n"/>
-      <c r="M118" s="3" t="n"/>
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0117</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>제품의 설계·생산·유통·유지보수 등 전 과정의 정보를 디지털화하여 관련 기업이 공유하는 체계로, 광속상거래라고도 불리는 것은?</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>WMS</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>CALS</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>CALS는 제품의 전 생애 주기 정보를 전자적으로 통합·공유하는 체계로 '광속상거래'로 불린다.</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>정보를 '빛의 속도'로 주고받는다는 별칭이 붙은 체계입니다.</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N118" s="3" t="n"/>
-      <c r="O118" s="3" t="n"/>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P118" s="3" t="n"/>
-      <c r="Q118" s="3" t="n"/>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – CALS</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n"/>
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="3" t="n"/>
-      <c r="D119" s="3" t="n"/>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
-      <c r="H119" s="3" t="n"/>
-      <c r="I119" s="3" t="n"/>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="n"/>
-      <c r="L119" s="3" t="n"/>
-      <c r="M119" s="3" t="n"/>
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0118</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>공동배송의 단점으로 볼 수 있는 것은?</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>참여 기업 간 영업 정보가 노출될 우려가 있다</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>물류 비용이 줄어든다</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>교통 혼잡과 대기오염이 줄어든다</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>차량 적재율이 높아진다</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>공동배송은 효율이 높지만 배송 순서 조정이 어렵고 거래처·물량 같은 영업 정보가 노출될 수 있다.</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>경쟁 관계의 회사들이 한 차를 함께 쓸 때 걱정할 만한 점입니다.</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N119" s="3" t="n"/>
-      <c r="O119" s="3" t="n"/>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P119" s="3" t="n"/>
-      <c r="Q119" s="3" t="n"/>
+      <c r="Q119" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 공동수배송의 장단점</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="3" t="n"/>
-      <c r="C120" s="3" t="n"/>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="n"/>
-      <c r="J120" s="3" t="n"/>
-      <c r="K120" s="3" t="n"/>
-      <c r="L120" s="3" t="n"/>
-      <c r="M120" s="3" t="n"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0119</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>한 차량이 정해진 경로를 돌며 여러 공급처의 화물을 조금씩 모아 오는 집하 방식은?</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>밀크런</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>허브 앤 스포크</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>직송 방식</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>밀크런은 우유 배달처럼 정해진 경로를 돌며 여러 곳의 화물을 모으는(또는 배송하는) 방식이다.</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>정해진 순서로 여러 곳을 돌며 조금씩 모으는 방식으로, 한곳에서 바로 분류·출고하는 방식과는 다릅니다.</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N120" s="3" t="n"/>
-      <c r="O120" s="3" t="n"/>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P120" s="3" t="n"/>
-      <c r="Q120" s="3" t="n"/>
+      <c r="Q120" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 일반 이론 – 순회 집하(Milk run) · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n"/>
-      <c r="B121" s="3" t="n"/>
-      <c r="C121" s="3" t="n"/>
-      <c r="D121" s="3" t="n"/>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
-      <c r="H121" s="3" t="n"/>
-      <c r="I121" s="3" t="n"/>
-      <c r="J121" s="3" t="n"/>
-      <c r="K121" s="3" t="n"/>
-      <c r="L121" s="3" t="n"/>
-      <c r="M121" s="3" t="n"/>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0120</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>하나의 주파수를 여러 사용자가 함께 쓰는 무선 통신으로, 차량 운행 관리에 쓰이는 시스템은?</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>TRS는 중계국의 주파수를 여러 이용자가 공동으로 사용하는 무선 통신으로, 차량과 사무실 간 음성·데이터 통신에 쓰인다.</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>무전기처럼 여러 차량과 사무실이 같은 통신망을 나누어 쓰는 방식입니다.</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N121" s="3" t="n"/>
-      <c r="O121" s="3" t="n"/>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P121" s="3" t="n"/>
-      <c r="Q121" s="3" t="n"/>
+      <c r="Q121" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – TRS · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n"/>
-      <c r="B122" s="3" t="n"/>
-      <c r="C122" s="3" t="n"/>
-      <c r="D122" s="3" t="n"/>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n"/>
-      <c r="G122" s="3" t="n"/>
-      <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="n"/>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="n"/>
-      <c r="L122" s="3" t="n"/>
-      <c r="M122" s="3" t="n"/>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0121</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>화물차에 GPS를 활용할 때의 효과로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>화물 포장이 필요 없어진다</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>운전자가 교통법규를 지키지 않아도 된다</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>차량 연료가 필요 없어진다</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>차량 위치를 실시간 파악해 빈 차 운행을 줄이고 도착 시간을 고객에게 안내할 수 있다</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>GPS로 차량 위치를 알면 가까운 차를 배차해 공차를 줄이고, 고객에게 정확한 도착 예정 시간을 알릴 수 있다.</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>위치 정보를 알면 배차와 고객 안내에 어떤 도움이 될까요?</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N122" s="3" t="n"/>
-      <c r="O122" s="3" t="n"/>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P122" s="3" t="n"/>
-      <c r="Q122" s="3" t="n"/>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – GPS 도입 효과</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n"/>
-      <c r="B123" s="3" t="n"/>
-      <c r="C123" s="3" t="n"/>
-      <c r="D123" s="3" t="n"/>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="n"/>
-      <c r="L123" s="3" t="n"/>
-      <c r="M123" s="3" t="n"/>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0122</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>국제 표준 상품 바코드(GS1 바코드)에서 우리나라에 부여된 국가 코드는?</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>GS1 체계에서 대한민국의 국가 코드는 880이다. 490은 일본, 690은 중국, 750은 멕시코 계열 코드이다.</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>우리나라 상품 포장 뒤 바코드 아래 숫자의 맨 앞자리를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N123" s="3" t="n"/>
-      <c r="O123" s="3" t="n"/>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P123" s="3" t="n"/>
-      <c r="Q123" s="3" t="n"/>
+      <c r="Q123" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: GS1 Korea 국가코드 880 (일반 상식, 원문 미대조)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
-      <c r="D124" s="3" t="n"/>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="3" t="n"/>
-      <c r="K124" s="3" t="n"/>
-      <c r="L124" s="3" t="n"/>
-      <c r="M124" s="3" t="n"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0123</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>가로·세로 두 방향으로 정보를 담아 일반 바코드보다 훨씬 많은 정보를 저장할 수 있는 것은?</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>2차원 바코드(QR코드 등)</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>OCR 문자</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>1차원 바코드</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>자기띠 카드</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>1차원 바코드는 가로 방향으로만 정보를 담지만, QR코드 같은 2차원 바코드는 두 방향으로 많은 정보를 담는다.</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>정보를 담는 방향의 수를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N124" s="3" t="n"/>
-      <c r="O124" s="3" t="n"/>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P124" s="3" t="n"/>
-      <c r="Q124" s="3" t="n"/>
+      <c r="Q124" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 정보 기술 일반 – 바코드 종류</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n"/>
-      <c r="B125" s="3" t="n"/>
-      <c r="C125" s="3" t="n"/>
-      <c r="D125" s="3" t="n"/>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="n"/>
-      <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="n"/>
-      <c r="L125" s="3" t="n"/>
-      <c r="M125" s="3" t="n"/>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0124</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>화물차의 전체 주행 거리 가운데 실제로 화물을 싣고 달린 거리의 비율을 무엇이라 하는가?</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>실차율</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>적재율</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>가동률</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>회전율</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>실차율은 총 주행거리 중 화물을 싣고 운행한 거리의 비율로, 높을수록 빈 차 운행이 적다.</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>빈 차가 아닌 상태로 달린 '거리'에 주목하세요. 날짜 기준 지표와 구분합니다.</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N125" s="3" t="n"/>
-      <c r="O125" s="3" t="n"/>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P125" s="3" t="n"/>
-      <c r="Q125" s="3" t="n"/>
+      <c r="Q125" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 운송 효율 지표</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n"/>
-      <c r="B126" s="3" t="n"/>
-      <c r="C126" s="3" t="n"/>
-      <c r="D126" s="3" t="n"/>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
-      <c r="H126" s="3" t="n"/>
-      <c r="I126" s="3" t="n"/>
-      <c r="J126" s="3" t="n"/>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="3" t="n"/>
-      <c r="M126" s="3" t="n"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0125</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>일정 기간 동안 화물차가 실제로 운행한 일수의 비율을 나타내는 지표는?</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>공차율</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>가동률</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>적재율</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>실차율</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>가동률은 일정 기간 중 차량이 실제로 운행(가동)한 일수의 비율이다.</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>거리가 아니라 '날짜' 기준 지표입니다.</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N126" s="3" t="n"/>
-      <c r="O126" s="3" t="n"/>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P126" s="3" t="n"/>
-      <c r="Q126" s="3" t="n"/>
+      <c r="Q126" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 운송 효율 지표</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
-      <c r="D127" s="3" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
-      <c r="J127" s="3" t="n"/>
-      <c r="K127" s="3" t="n"/>
-      <c r="L127" s="3" t="n"/>
-      <c r="M127" s="3" t="n"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0126</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>운송 효율을 높이기 위해 낮추어야 하는 지표는?</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>적재율</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>가동률</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>실차율</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>공차 거리율</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>공차 거리율은 빈 차로 달린 거리의 비율이므로 낮을수록 효율적이며, 나머지는 높을수록 좋다.</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>화물 없이 달리는 것은 비용만 드는 운행입니다.</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N127" s="3" t="n"/>
-      <c r="O127" s="3" t="n"/>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P127" s="3" t="n"/>
-      <c r="Q127" s="3" t="n"/>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 운송 효율 지표</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="3" t="n"/>
-      <c r="C128" s="3" t="n"/>
-      <c r="D128" s="3" t="n"/>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="n"/>
-      <c r="L128" s="3" t="n"/>
-      <c r="M128" s="3" t="n"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0127</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>자가용 화물차와 비교한 영업용 화물차 운송의 장점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>수요 변동에 따라 필요한 만큼 이용할 수 있어 설비 투자가 필요 없다</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>화주 회사의 작업 체계와 완전히 일치시키기 쉽다</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>운전자 관리를 화주가 직접 할 수 있다</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>긴급 상황에 화주가 마음대로 차량을 동원할 수 있다</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>영업용은 필요할 때만 이용해 차량·인력 투자 부담이 없다. 직접 통제·긴급 대응·작업 일관성은 자가용의 장점이다.</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>차를 '소유'하는 것과 '빌려 쓰는' 것의 차이를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N128" s="3" t="n"/>
-      <c r="O128" s="3" t="n"/>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P128" s="3" t="n"/>
-      <c r="Q128" s="3" t="n"/>
+      <c r="Q128" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 자가용과 영업용 트럭 운송 비교</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="3" t="n"/>
-      <c r="C129" s="3" t="n"/>
-      <c r="D129" s="3" t="n"/>
-      <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="n"/>
-      <c r="L129" s="3" t="n"/>
-      <c r="M129" s="3" t="n"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0128</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>개인 소유의 화물차를 운송회사 명의로 등록하고 영업하는 우리나라 화물운송 시장의 관행은?</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>리스제</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>공영제</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>직영제</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>지입제</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>지입제는 차주 개인이 소유한 차량을 운송사업자 명의로 등록해 영업하는 형태로, 운송시장 구조 문제로 지적된다.</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>차량의 실제 주인과 등록 명의가 서로 다른 구조입니다.</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N129" s="3" t="n"/>
-      <c r="O129" s="3" t="n"/>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P129" s="3" t="n"/>
-      <c r="Q129" s="3" t="n"/>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 화물운송산업의 문제점</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n"/>
-      <c r="B130" s="3" t="n"/>
-      <c r="C130" s="3" t="n"/>
-      <c r="D130" s="3" t="n"/>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="n"/>
-      <c r="K130" s="3" t="n"/>
-      <c r="L130" s="3" t="n"/>
-      <c r="M130" s="3" t="n"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0129</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>택배 이용 고객이 흔히 제기하는 불만 사항으로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>화물이 파손되거나 늦게 도착한 것</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>연락 없이 방문하고 그냥 가 버린 것</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>불친절한 말투와 태도</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>도착 전에 미리 연락하고 약속 시간에 배달한 것</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>사전 연락과 시간 약속 준수는 고객이 원하는 서비스이며, 무연락 방문·파손·지연·불친절이 주요 불만이다.</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>고객이 칭찬할 만한 행동을 찾으세요.</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N130" s="3" t="n"/>
-      <c r="O130" s="3" t="n"/>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P130" s="3" t="n"/>
-      <c r="Q130" s="3" t="n"/>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 고객 불만 사항</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n"/>
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
-      <c r="D131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="3" t="n"/>
-      <c r="K131" s="3" t="n"/>
-      <c r="L131" s="3" t="n"/>
-      <c r="M131" s="3" t="n"/>
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0130</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>택배 집하 시 운송장 작성에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>받는 사람 연락처는 생략해도 된다</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>품명·수량·물품 가액을 정확히 적게 하여 사고 시 배상 기준이 되게 한다</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>품명은 '기타'로 통일해 적는다</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>가액은 적지 않는 것이 고객에게 유리하다</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>운송장은 운송 계약의 증빙이며, 품명·수량·가액이 정확해야 취급 주의와 사고 배상이 제대로 이루어진다.</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>사고가 났을 때 무엇을 보고 배상액을 정할지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N131" s="3" t="n"/>
-      <c r="O131" s="3" t="n"/>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P131" s="3" t="n"/>
-      <c r="Q131" s="3" t="n"/>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 운송장 기재 요령</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n"/>
-      <c r="B132" s="3" t="n"/>
-      <c r="C132" s="3" t="n"/>
-      <c r="D132" s="3" t="n"/>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
-      <c r="J132" s="3" t="n"/>
-      <c r="K132" s="3" t="n"/>
-      <c r="L132" s="3" t="n"/>
-      <c r="M132" s="3" t="n"/>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0131</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>택배 배달 순서를 정할 때 우선적으로 고려할 화물로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>고객과 시간을 약속한 화물이나 신선식품처럼 시간이 급한 화물</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>운송장 번호가 가장 빠른 화물</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>부피가 가장 작은 화물</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>배달원 집에서 가장 가까운 화물</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>시간 약속 화물과 신선·긴급 화물은 늦으면 가치 손실과 불만이 크므로 우선 배달한다.</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>늦으면 손해가 가장 큰 화물이 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N132" s="3" t="n"/>
-      <c r="O132" s="3" t="n"/>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P132" s="3" t="n"/>
-      <c r="Q132" s="3" t="n"/>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 배달 요령</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n"/>
-      <c r="B133" s="3" t="n"/>
-      <c r="C133" s="3" t="n"/>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
-      <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="n"/>
-      <c r="L133" s="3" t="n"/>
-      <c r="M133" s="3" t="n"/>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0132</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>택배 집하 때 취급을 제한해야 하는 화물로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>포장이 잘 된 의류</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>완충재로 포장한 생활용품</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>상자에 담긴 서적</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>현금·유가증권처럼 분실 시 피해가 크고 약관상 취급이 제한된 물품</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>현금·유가증권·귀금속·위험물 등은 운송 약관상 취급이 제한되므로 정중히 설명하고 집하하지 않는다.</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>잃어버리면 되돌릴 수 없는 것이 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N133" s="3" t="n"/>
-      <c r="O133" s="3" t="n"/>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P133" s="3" t="n"/>
-      <c r="Q133" s="3" t="n"/>
+      <c r="Q133" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 집하 금지·제한 품목 (택배 표준약관 수탁거절 사유 참고)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n"/>
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="n"/>
-      <c r="L134" s="3" t="n"/>
-      <c r="M134" s="3" t="n"/>
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0133</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>물류비를 기능별로 나눌 때 해당하지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>하역비</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>조달물류비</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>운송비</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>보관비</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>운송·보관·포장·하역·물류정보관리비는 기능별 분류이고, 조달물류비는 영역별(조달·사내·판매·리버스) 분류에 속한다.</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>'어떤 활동'으로 나누는지 '어느 구간'으로 나누는지 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N134" s="3" t="n"/>
-      <c r="O134" s="3" t="n"/>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P134" s="3" t="n"/>
-      <c r="Q134" s="3" t="n"/>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류비 – 물류비의 분류 (기업물류비 산정지침 참고)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n"/>
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
-      <c r="D135" s="3" t="n"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="n"/>
-      <c r="L135" s="3" t="n"/>
-      <c r="M135" s="3" t="n"/>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0134</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>물류비를 지급 형태에 따라 나눌 때의 구분으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>자가물류비와 위탁물류비</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>조달물류비와 판매물류비</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>고정비와 매출원가</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>운송비와 보관비</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>지급 형태별로는 회사가 직접 수행해 쓴 자가물류비와 외부 업체에 지급한 위탁물류비로 나눈다.</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>물류를 '직접' 하는지 '맡기는지'로 나누는 방식입니다.</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N135" s="3" t="n"/>
-      <c r="O135" s="3" t="n"/>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P135" s="3" t="n"/>
-      <c r="Q135" s="3" t="n"/>
+      <c r="Q135" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류비 – 물류비의 분류 (기업물류비 산정지침 참고)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n"/>
-      <c r="B136" s="3" t="n"/>
-      <c r="C136" s="3" t="n"/>
-      <c r="D136" s="3" t="n"/>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
-      <c r="H136" s="3" t="n"/>
-      <c r="I136" s="3" t="n"/>
-      <c r="J136" s="3" t="n"/>
-      <c r="K136" s="3" t="n"/>
-      <c r="L136" s="3" t="n"/>
-      <c r="M136" s="3" t="n"/>
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0135</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>기업의 재무제표에 드러나는 물류비는 실제 물류비의 일부에 지나지 않는다는 뜻의 이론은?</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>규모의 경제</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>채찍 효과</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>파레토 법칙</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>물류비 빙산설(빙산 이론)</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>물류비는 다른 비용 항목에 섞여 있어 겉으로 보이는 부분은 일부뿐이라는 것을 빙산에 비유한 것이다.</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>보이는 비용보다 숨어 있는 비용이 훨씬 크다는 비유입니다.</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N136" s="3" t="n"/>
-      <c r="O136" s="3" t="n"/>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P136" s="3" t="n"/>
-      <c r="Q136" s="3" t="n"/>
+      <c r="Q136" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 일반 이론 – 물류비 빙산설(니시자와 오사무) · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n"/>
-      <c r="B137" s="3" t="n"/>
-      <c r="C137" s="3" t="n"/>
-      <c r="D137" s="3" t="n"/>
-      <c r="E137" s="3" t="n"/>
-      <c r="F137" s="3" t="n"/>
-      <c r="G137" s="3" t="n"/>
-      <c r="H137" s="3" t="n"/>
-      <c r="I137" s="3" t="n"/>
-      <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="n"/>
-      <c r="L137" s="3" t="n"/>
-      <c r="M137" s="3" t="n"/>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0136</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>화물을 파렛트나 컨테이너 같은 일정한 단위로 묶어 하역·운송·보관을 일관되게 하는 체계는?</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>적시생산(JIT)</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>밀크런</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>유닛로드 시스템(ULS)</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>유닛로드 시스템은 화물을 표준 단위로 묶어 기계화된 하역과 일관 수송을 가능하게 해 물류 효율을 높인다.</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>화물을 낱개가 아니라 한 덩어리로 다루는 체계입니다.</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N137" s="3" t="n"/>
-      <c r="O137" s="3" t="n"/>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P137" s="3" t="n"/>
-      <c r="Q137" s="3" t="n"/>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운송 합리화 – 유닛로드 시스템</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n"/>
-      <c r="B138" s="3" t="n"/>
-      <c r="C138" s="3" t="n"/>
-      <c r="D138" s="3" t="n"/>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="n"/>
-      <c r="L138" s="3" t="n"/>
-      <c r="M138" s="3" t="n"/>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0137</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>배송 차량이 정해진 지역을 정해진 경로와 시간에 따라 정기적으로 돌며 배송하는 방식은?</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>임시 배송</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>직송 배송</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>특송</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>루트 배송</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>루트 배송은 일정 지역의 배송처를 정해진 경로로 묶어 정기적으로 도는 방식으로 차량 운행 효율이 높다.</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>버스 노선처럼 미리 정한 길을 반복해서 도는 방식입니다.</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P138" s="3" t="n"/>
-      <c r="Q138" s="3" t="n"/>
+      <c r="Q138" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운송 합리화 – 수배송 효율화 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n"/>
-      <c r="B139" s="3" t="n"/>
-      <c r="C139" s="3" t="n"/>
-      <c r="D139" s="3" t="n"/>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
-      <c r="J139" s="3" t="n"/>
-      <c r="K139" s="3" t="n"/>
-      <c r="L139" s="3" t="n"/>
-      <c r="M139" s="3" t="n"/>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0138</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>한 화주의 화물만으로 컨테이너 1개를 채우지 못해 여러 화주의 화물을 함께 싣는 소량 화물은?</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>OOG 화물</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>벌크 화물</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>LCL 화물</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>FCL 화물</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>컨테이너 하나를 채우는 화물은 FCL, 채우지 못해 다른 화주 화물과 혼재하는 소량 화물은 LCL이다.</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>컨테이너를 꽉 채운 화물과 반대되는 개념입니다.</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N139" s="3" t="n"/>
-      <c r="O139" s="3" t="n"/>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P139" s="3" t="n"/>
-      <c r="Q139" s="3" t="n"/>
+      <c r="Q139" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 국제물류 일반 – FCL/LCL</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="3" t="n"/>
-      <c r="C140" s="3" t="n"/>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
-      <c r="J140" s="3" t="n"/>
-      <c r="K140" s="3" t="n"/>
-      <c r="L140" s="3" t="n"/>
-      <c r="M140" s="3" t="n"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0139</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>항만이나 터미널에서 소량(LCL) 화물을 모아 컨테이너에 혼재하거나 꺼내어 분류하는 장소는?</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>에이프런(Apron)</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>CY(컨테이너 야적장)</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>CFS(컨테이너 화물 조작장)</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>선석(Berth)</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>CFS는 LCL 화물의 적입·적출·혼재 작업을 하는 곳이고, CY는 컨테이너 자체를 쌓아 두고 인수·인도하는 곳이다.</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>'화물(Freight)'을 다루는 곳인지 '컨테이너'를 쌓는 곳인지 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N140" s="3" t="n"/>
-      <c r="O140" s="3" t="n"/>
+      <c r="O140" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P140" s="3" t="n"/>
-      <c r="Q140" s="3" t="n"/>
+      <c r="Q140" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 국제물류 일반 – CY/CFS</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n"/>
-      <c r="B141" s="3" t="n"/>
-      <c r="C141" s="3" t="n"/>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
-      <c r="J141" s="3" t="n"/>
-      <c r="K141" s="3" t="n"/>
-      <c r="L141" s="3" t="n"/>
-      <c r="M141" s="3" t="n"/>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0140</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>항만이 아닌 내륙에 설치되어 통관·컨테이너 보관·집화 기능을 하는 물류 기지는?</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>선석</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>보세운송 차량</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ICD</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>ICD는 내륙에 있는 컨테이너 기지로 통관, 보관, 집화·분류 기능을 하여 항만 혼잡을 줄인다.</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>항만의 혼잡을 덜기 위해 항만 밖에 둔 컨테이너 기지입니다.</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N141" s="3" t="n"/>
-      <c r="O141" s="3" t="n"/>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P141" s="3" t="n"/>
-      <c r="Q141" s="3" t="n"/>
+      <c r="Q141" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 국제 물류 – ICD (의왕ICD 등) · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="3" t="n"/>
-      <c r="C142" s="3" t="n"/>
-      <c r="D142" s="3" t="n"/>
-      <c r="E142" s="3" t="n"/>
-      <c r="F142" s="3" t="n"/>
-      <c r="G142" s="3" t="n"/>
-      <c r="H142" s="3" t="n"/>
-      <c r="I142" s="3" t="n"/>
-      <c r="J142" s="3" t="n"/>
-      <c r="K142" s="3" t="n"/>
-      <c r="L142" s="3" t="n"/>
-      <c r="M142" s="3" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0141</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>화물을 실은 트레일러나 트럭을 그대로 철도 화차에 실어 운송하는 복합운송 방식은?</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>피기백(Piggy-back)</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>드레이지(Drayage)</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>피시백(Fishy-back)</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>버디백(Birdy-back)</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>트럭+철도는 피기백, 트럭+선박은 피시백, 트럭+항공은 버디백이라 한다.</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>트럭과 기차의 결합입니다. 선박·항공과 결합한 방식의 이름과 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N142" s="3" t="n"/>
-      <c r="O142" s="3" t="n"/>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P142" s="3" t="n"/>
-      <c r="Q142" s="3" t="n"/>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 복합운송 일반 이론 – 결합 방식</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="3" t="n"/>
-      <c r="C143" s="3" t="n"/>
-      <c r="D143" s="3" t="n"/>
-      <c r="E143" s="3" t="n"/>
-      <c r="F143" s="3" t="n"/>
-      <c r="G143" s="3" t="n"/>
-      <c r="H143" s="3" t="n"/>
-      <c r="I143" s="3" t="n"/>
-      <c r="J143" s="3" t="n"/>
-      <c r="K143" s="3" t="n"/>
-      <c r="L143" s="3" t="n"/>
-      <c r="M143" s="3" t="n"/>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0142</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>복합운송에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>한 가지 운송 수단만 사용하는 운송이다</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>운송 구간마다 화주가 각각 계약하고 서류도 따로 받아야 한다</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>복합운송인이 전 구간에 대해 하나의 운송 책임을 지고 하나의 운송 증권을 발행한다</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>국내 운송에서만 이용된다</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>복합운송은 둘 이상의 운송 수단을 쓰되 복합운송인이 단일 계약·단일 책임·단일 증권으로 전 구간을 맡는다.</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>여러 수단이지만 '하나'로 묶이는 것이 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N143" s="3" t="n"/>
-      <c r="O143" s="3" t="n"/>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P143" s="3" t="n"/>
-      <c r="Q143" s="3" t="n"/>
+      <c r="Q143" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 복합운송 일반 이론 – 복합운송의 요건</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n"/>
-      <c r="B144" s="3" t="n"/>
-      <c r="C144" s="3" t="n"/>
-      <c r="D144" s="3" t="n"/>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="3" t="n"/>
-      <c r="G144" s="3" t="n"/>
-      <c r="H144" s="3" t="n"/>
-      <c r="I144" s="3" t="n"/>
-      <c r="J144" s="3" t="n"/>
-      <c r="K144" s="3" t="n"/>
-      <c r="L144" s="3" t="n"/>
-      <c r="M144" s="3" t="n"/>
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0143</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>해상 운송 도중 대륙을 철도로 가로질러 다시 해상으로 연결하는 국제 복합운송 경로를 무엇이라 하는가?</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>피더 서비스</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>환적항</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>랜드브리지(Land bridge)</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>랜드브리지는 대륙 횡단 철도를 바다와 바다를 잇는 다리처럼 이용하는 해-륙-해 복합운송이다(예: 시베리아 랜드브리지).</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>대륙 횡단 철도가 두 바다 사이를 잇는 역할을 하는 경로입니다.</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N144" s="3" t="n"/>
-      <c r="O144" s="3" t="n"/>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P144" s="3" t="n"/>
-      <c r="Q144" s="3" t="n"/>
+      <c r="Q144" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 복합운송 일반 이론 – 랜드브리지</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n"/>
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n"/>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="3" t="n"/>
-      <c r="L145" s="3" t="n"/>
-      <c r="M145" s="3" t="n"/>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0144</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>먼저 들어온 물품을 먼저 내보내 오래된 재고가 쌓이거나 변질되는 것을 막는 보관 원칙은?</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>후입선출</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>선입선출</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>동일성 원칙</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>높이 쌓기 원칙</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>선입선출은 입고 순서대로 출고하는 원칙으로, 유통기한이 있거나 상하기 쉬운 물품의 품질 저하와 재고 노후화를 막는다.</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>들어온 순서와 나가는 순서가 같다는 뜻의 말을 찾아보세요.</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N145" s="3" t="n"/>
-      <c r="O145" s="3" t="n"/>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P145" s="3" t="n"/>
-      <c r="Q145" s="3" t="n"/>
+      <c r="Q145" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류관리 교재 보관 원칙 일반 내용. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="3" t="n"/>
-      <c r="C146" s="3" t="n"/>
-      <c r="D146" s="3" t="n"/>
-      <c r="E146" s="3" t="n"/>
-      <c r="F146" s="3" t="n"/>
-      <c r="G146" s="3" t="n"/>
-      <c r="H146" s="3" t="n"/>
-      <c r="I146" s="3" t="n"/>
-      <c r="J146" s="3" t="n"/>
-      <c r="K146" s="3" t="n"/>
-      <c r="L146" s="3" t="n"/>
-      <c r="M146" s="3" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0145</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>창고 보관에서 출입 빈도가 높은 물품은 출입구 가까이에, 출입이 적은 물품은 먼 곳에 두는 원칙은?</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>명료성의 원칙</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>중량특성의 원칙</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>회전대응 보관의 원칙</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>형상특성의 원칙</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>회전대응 보관은 자주 드나드는 물품을 출입구 가까이 두어 이동 거리와 작업 시간을 줄이는 원칙이다. 중량특성은 무게, 형상특성은 모양, 명료성은 찾기 쉬운 표시에 따른 원칙이다.</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>물품이 얼마나 자주 '돌고 도는지'를 기준으로 삼는 원칙입니다.</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N146" s="3" t="n"/>
-      <c r="O146" s="3" t="n"/>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P146" s="3" t="n"/>
-      <c r="Q146" s="3" t="n"/>
+      <c r="Q146" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류관리 교재 보관 원칙 일반 내용. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="3" t="n"/>
-      <c r="C147" s="3" t="n"/>
-      <c r="D147" s="3" t="n"/>
-      <c r="E147" s="3" t="n"/>
-      <c r="F147" s="3" t="n"/>
-      <c r="G147" s="3" t="n"/>
-      <c r="H147" s="3" t="n"/>
-      <c r="I147" s="3" t="n"/>
-      <c r="J147" s="3" t="n"/>
-      <c r="K147" s="3" t="n"/>
-      <c r="L147" s="3" t="n"/>
-      <c r="M147" s="3" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0146</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>신선식품·의약품 등을 생산지에서 소비자에게 전달할 때까지 정해진 낮은 온도를 끊김 없이 유지하는 물류 체계는?</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>콜드체인</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>밀크런</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>모달시프트</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>콜드체인은 저온 유통 체계로, 냉장·냉동 상태를 전 과정에서 유지해 품질을 지킨다. 크로스도킹은 보관 없는 즉시 출고, 밀크런은 순회 집하, 모달시프트는 운송 수단 전환이다.</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>식품이나 백신이 상하지 않도록 운송 내내 무엇을 지켜야 하는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N147" s="3" t="n"/>
-      <c r="O147" s="3" t="n"/>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P147" s="3" t="n"/>
-      <c r="Q147" s="3" t="n"/>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 용어 일반 내용. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="3" t="n"/>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
-      <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
-      <c r="I148" s="3" t="n"/>
-      <c r="J148" s="3" t="n"/>
-      <c r="K148" s="3" t="n"/>
-      <c r="L148" s="3" t="n"/>
-      <c r="M148" s="3" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0147</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>물류 과정 중 마지막 거점에서 최종 소비자의 문 앞까지 상품을 전달하는 마지막 구간을 일컫는 말은?</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>퍼스트마일</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>간선 수송</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>인바운드 물류</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>라스트마일</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>라스트마일은 최종 배송 구간을 말하며, 고객이 직접 서비스를 체감하는 단계라 배송 품질이 중요하다. 간선 수송은 거점 사이의 장거리 운송을 뜻한다.</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>운송 경로를 달리기 경주로 본다면 결승선 직전 구간에 해당합니다.</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N148" s="3" t="n"/>
-      <c r="O148" s="3" t="n"/>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P148" s="3" t="n"/>
-      <c r="Q148" s="3" t="n"/>
+      <c r="Q148" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 용어 일반 내용. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n"/>
-      <c r="B149" s="3" t="n"/>
-      <c r="C149" s="3" t="n"/>
-      <c r="D149" s="3" t="n"/>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n"/>
-      <c r="G149" s="3" t="n"/>
-      <c r="H149" s="3" t="n"/>
-      <c r="I149" s="3" t="n"/>
-      <c r="J149" s="3" t="n"/>
-      <c r="K149" s="3" t="n"/>
-      <c r="L149" s="3" t="n"/>
-      <c r="M149" s="3" t="n"/>
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0148</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>서비스 품질을 평가하는 요소 중, 직원의 지식과 정중한 태도로 고객에게 믿음과 안심을 주는 능력을 뜻하는 것은?</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>유형성</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>신뢰성</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>확신성</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>반응성</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>확신성은 직원의 전문 지식·예의·능력으로 고객이 안심하게 하는 요소다. 신뢰성은 약속한 서비스를 정확히 제공하는 능력, 유형성은 눈에 보이는 시설·복장, 반응성은 신속히 도우려는 의지다.</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>고객이 '이 사람에게 맡기면 걱정 없겠다'라고 느끼게 하는 요소입니다.</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N149" s="3" t="n"/>
-      <c r="O149" s="3" t="n"/>
+      <c r="O149" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P149" s="3" t="n"/>
-      <c r="Q149" s="3" t="n"/>
+      <c r="Q149" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 서비스 품질 5차원(SERVQUAL) 일반 내용. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n"/>
-      <c r="B150" s="3" t="n"/>
-      <c r="C150" s="3" t="n"/>
-      <c r="D150" s="3" t="n"/>
-      <c r="E150" s="3" t="n"/>
-      <c r="F150" s="3" t="n"/>
-      <c r="G150" s="3" t="n"/>
-      <c r="H150" s="3" t="n"/>
-      <c r="I150" s="3" t="n"/>
-      <c r="J150" s="3" t="n"/>
-      <c r="K150" s="3" t="n"/>
-      <c r="L150" s="3" t="n"/>
-      <c r="M150" s="3" t="n"/>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0149</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>고객이 서비스를 받기 전에 갖는 기대 수준에 영향을 주는 요인으로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>주변 사람들의 이용 후기와 입소문</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>서비스를 제공하는 직원의 출신 지역</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>서비스를 이용했던 과거의 경험</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>회사가 광고나 안내로 약속한 내용</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>고객의 기대는 구전, 과거 경험, 개인적 필요, 회사가 내건 약속 등에 따라 형성된다. 직원의 출신 지역은 고객이 미리 알 수도 없고 기대 수준과 관계가 없다.</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>고객이 서비스를 받기 전에 실제로 듣거나 겪을 수 있는 정보인지 따져 보세요.</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N150" s="3" t="n"/>
-      <c r="O150" s="3" t="n"/>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P150" s="3" t="n"/>
-      <c r="Q150" s="3" t="n"/>
+      <c r="Q150" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 고객만족 교재 '고객 기대 형성 요인' 일반 내용. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="3" t="n"/>
-      <c r="C151" s="3" t="n"/>
-      <c r="D151" s="3" t="n"/>
-      <c r="E151" s="3" t="n"/>
-      <c r="F151" s="3" t="n"/>
-      <c r="G151" s="3" t="n"/>
-      <c r="H151" s="3" t="n"/>
-      <c r="I151" s="3" t="n"/>
-      <c r="J151" s="3" t="n"/>
-      <c r="K151" s="3" t="n"/>
-      <c r="L151" s="3" t="n"/>
-      <c r="M151" s="3" t="n"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0150</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>배송 실수로 불만을 가진 고객의 문제를 신속하고 성의 있게 해결했을 때 나타날 수 있는 현상으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>한 번 불만을 가진 고객은 어떻게 대응해도 다시 거래하지 않는다</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>문제가 해결되면 고객은 그 일을 곧바로 잊으므로 사후 연락은 필요 없다</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>실수를 인정하면 회사 이미지가 나빠지므로 원인을 고객 탓으로 돌리는 것이 좋다</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>처음부터 문제가 없었던 고객보다 오히려 회사를 더 신뢰하게 될 수도 있다</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>서비스 실패를 빠르고 정성껏 회복하면 고객이 오히려 더 높은 만족과 신뢰를 느끼는 경우가 있는데, 이를 서비스 회복의 역설이라 한다. 그래서 불만 처리는 고객을 지킬 기회가 된다.</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>위기를 잘 넘기면 관계가 오히려 깊어질 수 있다는 말을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N151" s="3" t="n"/>
-      <c r="O151" s="3" t="n"/>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
       <c r="P151" s="3" t="n"/>
-      <c r="Q151" s="3" t="n"/>
+      <c r="Q151" s="3" t="inlineStr">
+        <is>
+          <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 서비스 마케팅 '서비스 회복 패러독스' 일반 개념. 원문 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>

--- a/data/raw/문제_SERVICE.xlsx
+++ b/data/raw/문제_SERVICE.xlsx
@@ -6664,10 +6664,14 @@
       <c r="N77" s="3" t="n"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P77" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 직업의 의미</t>
@@ -6739,10 +6743,14 @@
       <c r="N78" s="3" t="n"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 바람직한 직업관</t>
@@ -6814,10 +6822,14 @@
       <c r="N79" s="3" t="n"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 잘못된 직업관</t>
@@ -6889,10 +6901,14 @@
       <c r="N80" s="3" t="n"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세</t>
@@ -6964,10 +6980,14 @@
       <c r="N81" s="3" t="n"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 · 교차 점검 반영</t>
@@ -7039,10 +7059,14 @@
       <c r="N82" s="3" t="n"/>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 직업 운전자의 기본자세 – 심신상태의 안정</t>
@@ -7114,10 +7138,14 @@
       <c r="N83" s="3" t="n"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스의 특징 · 교차 점검 반영</t>
@@ -7189,10 +7217,14 @@
       <c r="N84" s="3" t="n"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스의 특징</t>
@@ -7264,10 +7296,14 @@
       <c r="N85" s="3" t="n"/>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스의 특징</t>
@@ -7339,10 +7375,14 @@
       <c r="N86" s="3" t="n"/>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객의 욕구</t>
@@ -7414,10 +7454,14 @@
       <c r="N87" s="3" t="n"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객이 거래를 중단하는 이유</t>
@@ -7489,10 +7533,14 @@
       <c r="N88" s="3" t="n"/>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객만족의 중요성</t>
@@ -7564,10 +7612,14 @@
       <c r="N89" s="3" t="n"/>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P89" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객만족을 위한 3가지 품질</t>
@@ -7639,10 +7691,14 @@
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P90" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객만족을 위한 3가지 품질</t>
@@ -7714,10 +7770,14 @@
       <c r="N91" s="3" t="n"/>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P91" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 서비스 품질의 평가 기준 · 교차 점검 반영</t>
@@ -7789,10 +7849,14 @@
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: SERVQUAL 5차원(유형성·신뢰성·응답성·확신성·공감성) 일반 서비스 이론</t>
@@ -7864,10 +7928,14 @@
       <c r="N93" s="3" t="n"/>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 일반 고객서비스(CS) 이론 – 불만 고객 응대 기법</t>
@@ -7939,10 +8007,14 @@
       <c r="N94" s="3" t="n"/>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객 불만 처리 요령</t>
@@ -8014,10 +8086,14 @@
       <c r="N95" s="3" t="n"/>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P95" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 고객만족 – 고객의 개념</t>
@@ -8089,10 +8165,14 @@
       <c r="N96" s="3" t="n"/>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 인사의 종류</t>
@@ -8164,10 +8244,14 @@
       <c r="N97" s="3" t="n"/>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 표정과 시선</t>
@@ -8239,10 +8323,14 @@
       <c r="N98" s="3" t="n"/>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 복장과 용모</t>
@@ -8314,10 +8402,14 @@
       <c r="N99" s="3" t="n"/>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 기본 예절 – 전화 응대</t>
@@ -8389,10 +8481,14 @@
       <c r="N100" s="3" t="n"/>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운전자 수칙 – 화물 적재</t>
@@ -8464,10 +8560,14 @@
       <c r="N101" s="3" t="n"/>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운전자 수칙 – 운행 중 준수사항</t>
@@ -8539,10 +8639,14 @@
       <c r="N102" s="3" t="n"/>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 로지스틱스</t>
@@ -8614,10 +8718,14 @@
       <c r="N103" s="3" t="n"/>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류 개념의 변천</t>
@@ -8689,10 +8797,14 @@
       <c r="N104" s="3" t="n"/>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P104" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류의 역할</t>
@@ -8764,10 +8876,14 @@
       <c r="N105" s="3" t="n"/>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P105" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류의 중요성 · 교차 점검 반영</t>
@@ -8839,10 +8955,14 @@
       <c r="N106" s="3" t="n"/>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P106" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류관리의 목표</t>
@@ -8914,10 +9034,14 @@
       <c r="N107" s="3" t="n"/>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P107" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류의 영역 · 교차 점검 반영</t>
@@ -8989,10 +9113,14 @@
       <c r="N108" s="3" t="n"/>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P108" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 운송 관련 용어</t>
@@ -9064,10 +9192,14 @@
       <c r="N109" s="3" t="n"/>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P109" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 일반 이론 – 리드타임</t>
@@ -9139,10 +9271,14 @@
       <c r="N110" s="3" t="n"/>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P110" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 제3자 물류</t>
@@ -9214,10 +9350,14 @@
       <c r="N111" s="3" t="n"/>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P111" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 제3자 물류 기대효과</t>
@@ -9289,10 +9429,14 @@
       <c r="N112" s="3" t="n"/>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P112" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 제4자 물류 4단계</t>
@@ -9364,10 +9508,14 @@
       <c r="N113" s="3" t="n"/>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P113" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P113" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 공급망관리</t>
@@ -9439,10 +9587,14 @@
       <c r="N114" s="3" t="n"/>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P114" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – SCM 주요 기법 · 교차 점검 반영</t>
@@ -9514,10 +9666,14 @@
       <c r="N115" s="3" t="n"/>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P115" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P115" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – SCM 주요 기법</t>
@@ -9589,10 +9745,14 @@
       <c r="N116" s="3" t="n"/>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P116" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: SCM 일반 이론 – VMI · 교차 점검 반영</t>
@@ -9664,10 +9824,14 @@
       <c r="N117" s="3" t="n"/>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P117" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 물류 정보 시스템 · 교차 점검 반영</t>
@@ -9739,10 +9903,14 @@
       <c r="N118" s="3" t="n"/>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P118" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – CALS</t>
@@ -9814,10 +9982,14 @@
       <c r="N119" s="3" t="n"/>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P119" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P119" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – 공동수배송의 장단점</t>
@@ -9889,10 +10061,14 @@
       <c r="N120" s="3" t="n"/>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P120" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 일반 이론 – 순회 집하(Milk run) · 교차 점검 반영</t>
@@ -9964,10 +10140,14 @@
       <c r="N121" s="3" t="n"/>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P121" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – TRS · 교차 점검 반영</t>
@@ -10039,10 +10219,14 @@
       <c r="N122" s="3" t="n"/>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P122" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류의 이해 – GPS 도입 효과</t>
@@ -10114,10 +10298,14 @@
       <c r="N123" s="3" t="n"/>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P123" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: GS1 Korea 국가코드 880 (일반 상식, 원문 미대조)</t>
@@ -10189,10 +10377,14 @@
       <c r="N124" s="3" t="n"/>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P124" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 정보 기술 일반 – 바코드 종류</t>
@@ -10264,10 +10456,14 @@
       <c r="N125" s="3" t="n"/>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P125" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 운송 효율 지표</t>
@@ -10339,10 +10535,14 @@
       <c r="N126" s="3" t="n"/>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P126" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 운송 효율 지표</t>
@@ -10414,10 +10614,14 @@
       <c r="N127" s="3" t="n"/>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P127" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 운송 효율 지표</t>
@@ -10489,10 +10693,14 @@
       <c r="N128" s="3" t="n"/>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P128" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 자가용과 영업용 트럭 운송 비교</t>
@@ -10564,10 +10772,14 @@
       <c r="N129" s="3" t="n"/>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P129" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 화물운송 서비스 – 화물운송산업의 문제점</t>
@@ -10639,10 +10851,14 @@
       <c r="N130" s="3" t="n"/>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P130" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 고객 불만 사항</t>
@@ -10714,10 +10930,14 @@
       <c r="N131" s="3" t="n"/>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P131" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 운송장 기재 요령</t>
@@ -10789,10 +11009,14 @@
       <c r="N132" s="3" t="n"/>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P132" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 배달 요령</t>
@@ -10864,10 +11088,14 @@
       <c r="N133" s="3" t="n"/>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P133" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 택배 서비스 – 집하 금지·제한 품목 (택배 표준약관 수탁거절 사유 참고)</t>
@@ -10939,10 +11167,14 @@
       <c r="N134" s="3" t="n"/>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P134" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류비 – 물류비의 분류 (기업물류비 산정지침 참고)</t>
@@ -11014,10 +11246,14 @@
       <c r="N135" s="3" t="n"/>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P135" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 물류비 – 물류비의 분류 (기업물류비 산정지침 참고)</t>
@@ -11089,10 +11325,14 @@
       <c r="N136" s="3" t="n"/>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P136" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 일반 이론 – 물류비 빙산설(니시자와 오사무) · 교차 점검 반영</t>
@@ -11164,10 +11404,14 @@
       <c r="N137" s="3" t="n"/>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P137" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운송 합리화 – 유닛로드 시스템</t>
@@ -11239,10 +11483,14 @@
       <c r="N138" s="3" t="n"/>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P138" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 운송 합리화 – 수배송 효율화 · 교차 점검 반영</t>
@@ -11314,10 +11562,14 @@
       <c r="N139" s="3" t="n"/>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P139" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 국제물류 일반 – FCL/LCL</t>
@@ -11389,10 +11641,14 @@
       <c r="N140" s="3" t="n"/>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P140" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 국제물류 일반 – CY/CFS</t>
@@ -11464,10 +11720,14 @@
       <c r="N141" s="3" t="n"/>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P141" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 화물운송종사자격 교재 운송서비스편 국제 물류 – ICD (의왕ICD 등) · 교차 점검 반영</t>
@@ -11539,10 +11799,14 @@
       <c r="N142" s="3" t="n"/>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P142" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 복합운송 일반 이론 – 결합 방식</t>
@@ -11614,10 +11878,14 @@
       <c r="N143" s="3" t="n"/>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P143" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 복합운송 일반 이론 – 복합운송의 요건</t>
@@ -11689,10 +11957,14 @@
       <c r="N144" s="3" t="n"/>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P144" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 복합운송 일반 이론 – 랜드브리지</t>
@@ -11764,10 +12036,14 @@
       <c r="N145" s="3" t="n"/>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P145" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류관리 교재 보관 원칙 일반 내용. 원문 미확인</t>
@@ -11839,10 +12115,14 @@
       <c r="N146" s="3" t="n"/>
       <c r="O146" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P146" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류관리 교재 보관 원칙 일반 내용. 원문 미확인</t>
@@ -11914,10 +12194,14 @@
       <c r="N147" s="3" t="n"/>
       <c r="O147" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P147" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 용어 일반 내용. 원문 미확인</t>
@@ -11989,10 +12273,14 @@
       <c r="N148" s="3" t="n"/>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P148" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 물류 용어 일반 내용. 원문 미확인</t>
@@ -12064,10 +12352,14 @@
       <c r="N149" s="3" t="n"/>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P149" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 서비스 품질 5차원(SERVQUAL) 일반 내용. 원문 미확인</t>
@@ -12139,10 +12431,14 @@
       <c r="N150" s="3" t="n"/>
       <c r="O150" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P150" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 고객만족 교재 '고객 기대 형성 요인' 일반 내용. 원문 미확인</t>
@@ -12214,10 +12510,14 @@
       <c r="N151" s="3" t="n"/>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P151" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 서비스 마케팅 '서비스 회복 패러독스' 일반 개념. 원문 미확인</t>

--- a/data/raw/문제_SERVICE.xlsx
+++ b/data/raw/문제_SERVICE.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12525,954 +12525,5904 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n"/>
-      <c r="B152" s="3" t="n"/>
-      <c r="C152" s="3" t="n"/>
-      <c r="D152" s="3" t="n"/>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n"/>
-      <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="n"/>
-      <c r="I152" s="3" t="n"/>
-      <c r="J152" s="3" t="n"/>
-      <c r="K152" s="3" t="n"/>
-      <c r="L152" s="3" t="n"/>
-      <c r="M152" s="3" t="n"/>
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0151</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>직업이 가지는 의미 가운데 '사회의 한 구성원으로서 맡은 역할을 다하고 공동체 발전에 이바지한다'는 것에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>경제적 의미</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>심리적 의미</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>법률적 의미</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>사회적 의미</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>직업은 경제적 의미(생계), 심리적 의미(자아실현), 사회적 의미(역할 분담·사회 기여)를 가진다. 공동체에 이바지하는 측면은 사회적 의미이다.</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>혼자가 아니라 여럿이 함께 사는 집단 속에서의 역할을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N152" s="3" t="n"/>
-      <c r="O152" s="3" t="n"/>
-      <c r="P152" s="3" t="n"/>
-      <c r="Q152" s="3" t="n"/>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q152" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n"/>
-      <c r="B153" s="3" t="n"/>
-      <c r="C153" s="3" t="n"/>
-      <c r="D153" s="3" t="n"/>
-      <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
-      <c r="G153" s="3" t="n"/>
-      <c r="H153" s="3" t="n"/>
-      <c r="I153" s="3" t="n"/>
-      <c r="J153" s="3" t="n"/>
-      <c r="K153" s="3" t="n"/>
-      <c r="L153" s="3" t="n"/>
-      <c r="M153" s="3" t="n"/>
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0152</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>바람직한 직업관 가운데 자신의 일이 사회와 다른 사람에게 꼭 필요한 역할을 한다고 여기고 맡은 바 책임을 다하려는 의식은?</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>생계 수단적 직업관</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>지위 지향적 직업관</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>직분의식</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>차별적 직업관</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>직분의식은 자기 직업이 사회에서 맡은 몫(직분)을 인식하고 책임을 다하려는 바람직한 직업의식이다. 나머지는 잘못된 직업관이다.</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>나머지 보기는 교재에서 잘못된 직업관이나 차별 의식으로 분류되는 것들입니다.</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N153" s="3" t="n"/>
-      <c r="O153" s="3" t="n"/>
-      <c r="P153" s="3" t="n"/>
-      <c r="Q153" s="3" t="n"/>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n"/>
-      <c r="B154" s="3" t="n"/>
-      <c r="C154" s="3" t="n"/>
-      <c r="D154" s="3" t="n"/>
-      <c r="E154" s="3" t="n"/>
-      <c r="F154" s="3" t="n"/>
-      <c r="G154" s="3" t="n"/>
-      <c r="H154" s="3" t="n"/>
-      <c r="I154" s="3" t="n"/>
-      <c r="J154" s="3" t="n"/>
-      <c r="K154" s="3" t="n"/>
-      <c r="L154" s="3" t="n"/>
-      <c r="M154" s="3" t="n"/>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0153</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자의 사명으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>다른 사람의 생명도 내 생명처럼 소중히 여기며 안전하게 운전한다</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>운송 횟수를 늘려 수입을 최대한 높인다</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>내 차량과 화물만 안전하면 다른 차는 신경 쓰지 않는다</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>운전 기술이 뛰어나면 법규는 상황에 따라 무시해도 된다</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자는 사람과 화물을 안전하게 옮기는 공공적 역할을 하므로 타인의 생명을 존중하는 안전운전이 가장 기본적인 사명이다.</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>돈보다 먼저 지켜야 할 것이 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N154" s="3" t="n"/>
-      <c r="O154" s="3" t="n"/>
-      <c r="P154" s="3" t="n"/>
-      <c r="Q154" s="3" t="n"/>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n"/>
-      <c r="B155" s="3" t="n"/>
-      <c r="C155" s="3" t="n"/>
-      <c r="D155" s="3" t="n"/>
-      <c r="E155" s="3" t="n"/>
-      <c r="F155" s="3" t="n"/>
-      <c r="G155" s="3" t="n"/>
-      <c r="H155" s="3" t="n"/>
-      <c r="I155" s="3" t="n"/>
-      <c r="J155" s="3" t="n"/>
-      <c r="K155" s="3" t="n"/>
-      <c r="L155" s="3" t="n"/>
-      <c r="M155" s="3" t="n"/>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0154</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>운송 중 화주의 화물을 몰래 빼돌리거나 운임을 부풀려 청구하지 않아야 한다는 것은 어떤 직업윤리와 가장 관련이 깊은가?</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>창의성</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>경쟁의식</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>정직과 신용</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>개인주의</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>화물과 운임을 속이지 않는 것은 거짓 없이 믿음을 지키는 정직·신용의 윤리에 해당한다.</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>거래 상대가 나를 믿고 맡길 수 있게 하는 덕목입니다.</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N155" s="3" t="n"/>
-      <c r="O155" s="3" t="n"/>
-      <c r="P155" s="3" t="n"/>
-      <c r="Q155" s="3" t="n"/>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q155" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n"/>
-      <c r="B156" s="3" t="n"/>
-      <c r="C156" s="3" t="n"/>
-      <c r="D156" s="3" t="n"/>
-      <c r="E156" s="3" t="n"/>
-      <c r="F156" s="3" t="n"/>
-      <c r="G156" s="3" t="n"/>
-      <c r="H156" s="3" t="n"/>
-      <c r="I156" s="3" t="n"/>
-      <c r="J156" s="3" t="n"/>
-      <c r="K156" s="3" t="n"/>
-      <c r="L156" s="3" t="n"/>
-      <c r="M156" s="3" t="n"/>
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0155</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>거만한 태도를 보이는 고객을 응대하는 방법으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>똑같이 거만한 태도로 맞서 기선을 잡는다</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>대화를 짧게 끊고 못 본 척한다</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>고객의 말 중 틀린 부분을 하나하나 지적한다</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>정중하게 대하면서 고객의 자존심을 세워 주고 하고 싶은 말을 충분히 들어 준다</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>거만한 고객은 인정받고 싶은 욕구가 강하므로 정중한 태도로 자존심을 세워 주면 오히려 쉽게 응대할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>이런 고객이 가장 바라는 것은 '인정받는 느낌'입니다.</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N156" s="3" t="n"/>
-      <c r="O156" s="3" t="n"/>
-      <c r="P156" s="3" t="n"/>
-      <c r="Q156" s="3" t="n"/>
+      <c r="O156" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q156" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n"/>
-      <c r="B157" s="3" t="n"/>
-      <c r="C157" s="3" t="n"/>
-      <c r="D157" s="3" t="n"/>
-      <c r="E157" s="3" t="n"/>
-      <c r="F157" s="3" t="n"/>
-      <c r="G157" s="3" t="n"/>
-      <c r="H157" s="3" t="n"/>
-      <c r="I157" s="3" t="n"/>
-      <c r="J157" s="3" t="n"/>
-      <c r="K157" s="3" t="n"/>
-      <c r="L157" s="3" t="n"/>
-      <c r="M157" s="3" t="n"/>
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0156</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>의심이 많은 고객을 응대하는 방법으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>자신 있는 말투로 무조건 믿으라고 한다</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>질문이 많으면 대답을 줄이고 서둘러 마무리한다</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>분명한 근거나 자료를 보여 주어 고객이 스스로 확신하도록 돕는다</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>다른 고객도 다 괜찮다고 했다며 넘어간다</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>의심이 많은 고객에게는 말보다 확인할 수 있는 증거(운송장 조회 내역, 사진 등)를 제시하는 것이 효과적이다.</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>말로 설득하기보다 눈으로 확인할 수 있게 해 주세요.</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N157" s="3" t="n"/>
-      <c r="O157" s="3" t="n"/>
-      <c r="P157" s="3" t="n"/>
-      <c r="Q157" s="3" t="n"/>
+      <c r="O157" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q157" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n"/>
-      <c r="B158" s="3" t="n"/>
-      <c r="C158" s="3" t="n"/>
-      <c r="D158" s="3" t="n"/>
-      <c r="E158" s="3" t="n"/>
-      <c r="F158" s="3" t="n"/>
-      <c r="G158" s="3" t="n"/>
-      <c r="H158" s="3" t="n"/>
-      <c r="I158" s="3" t="n"/>
-      <c r="J158" s="3" t="n"/>
-      <c r="K158" s="3" t="n"/>
-      <c r="L158" s="3" t="n"/>
-      <c r="M158" s="3" t="n"/>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0157</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>결정을 쉽게 내리지 못하는 우유부단한 고객을 응대하는 방법으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>고객이 결정할 때까지 아무 말 없이 기다리기만 한다</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>직원이 마음대로 정해서 처리해 버린다</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>결정을 못 하면 다음에 다시 오라고 돌려보낸다</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>몇 가지 선택지를 알기 쉽게 정리해 제시하고 결정을 도와준다</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>우유부단한 고객에게는 비교하기 쉬운 몇 가지 안을 제시하고 장단점을 설명해 스스로 결정하도록 돕는다.</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>고르기 어려워하는 사람에게 필요한 것은 '정리된 길잡이'입니다.</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N158" s="3" t="n"/>
-      <c r="O158" s="3" t="n"/>
-      <c r="P158" s="3" t="n"/>
-      <c r="Q158" s="3" t="n"/>
+      <c r="O158" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="3" t="n"/>
-      <c r="C159" s="3" t="n"/>
-      <c r="D159" s="3" t="n"/>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n"/>
-      <c r="G159" s="3" t="n"/>
-      <c r="H159" s="3" t="n"/>
-      <c r="I159" s="3" t="n"/>
-      <c r="J159" s="3" t="n"/>
-      <c r="K159" s="3" t="n"/>
-      <c r="L159" s="3" t="n"/>
-      <c r="M159" s="3" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0158</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>성격이 급해 빠른 처리를 원하는 고객을 응대하는 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>처음부터 자세한 설명을 길게 되풀이한다</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>요점만 간단히 말하고 신속하게 처리한다</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>천천히 해도 된다며 고객을 달랜다</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>다른 고객 응대를 모두 마친 뒤 마지막에 처리한다</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>급한 고객에게는 군더더기 없는 설명과 빠른 처리가 만족을 높인다.</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>이 고객이 가장 아까워하는 것은 시간입니다.</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N159" s="3" t="n"/>
-      <c r="O159" s="3" t="n"/>
-      <c r="P159" s="3" t="n"/>
-      <c r="Q159" s="3" t="n"/>
+      <c r="O159" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n"/>
-      <c r="B160" s="3" t="n"/>
-      <c r="C160" s="3" t="n"/>
-      <c r="D160" s="3" t="n"/>
-      <c r="E160" s="3" t="n"/>
-      <c r="F160" s="3" t="n"/>
-      <c r="G160" s="3" t="n"/>
-      <c r="H160" s="3" t="n"/>
-      <c r="I160" s="3" t="n"/>
-      <c r="J160" s="3" t="n"/>
-      <c r="K160" s="3" t="n"/>
-      <c r="L160" s="3" t="n"/>
-      <c r="M160" s="3" t="n"/>
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0159</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>자기가 잘 안다며 전문가처럼 행동하는 고객을 응대하는 방법으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>고객이 틀린 부분을 다른 사람 앞에서 바로 바로잡아 망신을 준다</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>대화를 피하고 다른 직원에게 넘긴다</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>고객의 지식을 인정해 주면서 정확한 정보를 차분히 설명한다</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>틀린 정보라도 고객 말에 그대로 동의해 준다</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>아는 체하는 고객은 체면을 중시하므로 먼저 인정해 준 뒤 정확한 내용을 부드럽게 알려 주어야 한다.</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>체면을 지켜 주는 것과 사실을 바로 알리는 것을 함께 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N160" s="3" t="n"/>
-      <c r="O160" s="3" t="n"/>
-      <c r="P160" s="3" t="n"/>
-      <c r="Q160" s="3" t="n"/>
+      <c r="O160" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q160" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n"/>
-      <c r="B161" s="3" t="n"/>
-      <c r="C161" s="3" t="n"/>
-      <c r="D161" s="3" t="n"/>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="n"/>
-      <c r="H161" s="3" t="n"/>
-      <c r="I161" s="3" t="n"/>
-      <c r="J161" s="3" t="n"/>
-      <c r="K161" s="3" t="n"/>
-      <c r="L161" s="3" t="n"/>
-      <c r="M161" s="3" t="n"/>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0160</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>고객 불만 처리 단계의 일반적인 순서로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>해결책 제시 → 경청 → 사과 → 원인 파악 → 결과 확인</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>경청 → 공감·사과 → 원인 파악 → 해결책 제시·처리 → 결과 확인</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>원인 파악 → 변명 → 경청 → 처리 → 결과 확인</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>사과 → 처리 → 경청 → 원인 파악 → 결과 확인</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>먼저 끝까지 듣고 공감·사과로 감정을 가라앉힌 뒤, 원인을 파악해 해결하고 만족 여부를 확인하는 순서가 일반적이다.</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>감정을 먼저 다루고, 문제는 그다음에 다룹니다.</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N161" s="3" t="n"/>
-      <c r="O161" s="3" t="n"/>
-      <c r="P161" s="3" t="n"/>
-      <c r="Q161" s="3" t="n"/>
+      <c r="O161" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q161" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="3" t="n"/>
-      <c r="C162" s="3" t="n"/>
-      <c r="D162" s="3" t="n"/>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="n"/>
-      <c r="H162" s="3" t="n"/>
-      <c r="I162" s="3" t="n"/>
-      <c r="J162" s="3" t="n"/>
-      <c r="K162" s="3" t="n"/>
-      <c r="L162" s="3" t="n"/>
-      <c r="M162" s="3" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0161</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>불만 처리 과정 중 '원인 파악' 단계에서 하는 일로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>고객 말이 사실인지 따지며 증거부터 내놓으라고 한다</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>정중히 질문하여 문제가 생긴 경위와 고객이 원하는 해결 방향을 확인한다</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>원인과 상관없이 보상금부터 제시한다</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>담당자를 찾아 책임을 그쪽으로 돌린다</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>원인 파악 단계에서는 고객을 추궁하지 않고 질문을 통해 사실관계와 고객의 요구를 정확히 알아낸다.</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>따지는 질문과 알아보는 질문은 다릅니다.</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N162" s="3" t="n"/>
-      <c r="O162" s="3" t="n"/>
-      <c r="P162" s="3" t="n"/>
-      <c r="Q162" s="3" t="n"/>
+      <c r="O162" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q162" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n"/>
-      <c r="B163" s="3" t="n"/>
-      <c r="C163" s="3" t="n"/>
-      <c r="D163" s="3" t="n"/>
-      <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
-      <c r="G163" s="3" t="n"/>
-      <c r="H163" s="3" t="n"/>
-      <c r="I163" s="3" t="n"/>
-      <c r="J163" s="3" t="n"/>
-      <c r="K163" s="3" t="n"/>
-      <c r="L163" s="3" t="n"/>
-      <c r="M163" s="3" t="n"/>
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0162</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>불만을 제기한 고객에게 해서는 안 되는 말은?</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>그건 제 담당이 아니라서 저는 모릅니다</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>불편을 드려 정말 죄송합니다</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>제가 바로 확인해서 다시 연락드리겠습니다</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>말씀해 주셔서 감사합니다</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>고객에게는 직원 한 사람이 곧 회사이므로 담당이 아니라며 책임을 피하는 말은 불만을 더 키운다.</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>고객 눈에는 직원 한 명이 회사 전체로 보입니다.</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N163" s="3" t="n"/>
-      <c r="O163" s="3" t="n"/>
-      <c r="P163" s="3" t="n"/>
-      <c r="Q163" s="3" t="n"/>
+      <c r="O163" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q163" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="3" t="n"/>
-      <c r="C164" s="3" t="n"/>
-      <c r="D164" s="3" t="n"/>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
-      <c r="H164" s="3" t="n"/>
-      <c r="I164" s="3" t="n"/>
-      <c r="J164" s="3" t="n"/>
-      <c r="K164" s="3" t="n"/>
-      <c r="L164" s="3" t="n"/>
-      <c r="M164" s="3" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0163</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>불만을 느낀 고객의 행동에 대한 일반적인 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>불만족한 경험은 만족한 경험보다 더 많은 사람에게 퍼지는 경향이 있다</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>불만족한 고객은 대부분 회사에 직접 불만을 말한다</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>불만족한 경험은 주변에 거의 이야기하지 않는다</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>한 번 불만을 느낀 고객은 어떤 조치를 해도 다시 거래하지 않는다</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>나쁜 경험은 좋은 경험보다 더 널리 입소문이 나므로 불만을 초기에 잘 처리해야 한다.</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>좋은 소문과 나쁜 소문 중 어느 것이 더 빨리 퍼지는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N164" s="3" t="n"/>
-      <c r="O164" s="3" t="n"/>
-      <c r="P164" s="3" t="n"/>
-      <c r="Q164" s="3" t="n"/>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q164" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="3" t="n"/>
-      <c r="C165" s="3" t="n"/>
-      <c r="D165" s="3" t="n"/>
-      <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="n"/>
-      <c r="H165" s="3" t="n"/>
-      <c r="I165" s="3" t="n"/>
-      <c r="J165" s="3" t="n"/>
-      <c r="K165" s="3" t="n"/>
-      <c r="L165" s="3" t="n"/>
-      <c r="M165" s="3" t="n"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0164</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>'서비스 실패'의 뜻으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>제공된 서비스가 고객의 기대 수준에 미치지 못해 고객이 불만을 느끼는 상태</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>회사의 매출 목표를 달성하지 못한 상태</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>고객이 서비스 요금을 내지 않은 상태</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>직원이 정해진 근무 시간을 지키지 못한 상태</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>서비스 실패는 고객이 기대한 것보다 낮은 수준의 서비스를 경험하는 것으로, 판단 기준은 고객의 기대이다.</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>판단의 기준이 회사가 아니라 누구인지 보세요.</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N165" s="3" t="n"/>
-      <c r="O165" s="3" t="n"/>
-      <c r="P165" s="3" t="n"/>
-      <c r="Q165" s="3" t="n"/>
+      <c r="O165" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q165" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="3" t="n"/>
-      <c r="C166" s="3" t="n"/>
-      <c r="D166" s="3" t="n"/>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="n"/>
-      <c r="G166" s="3" t="n"/>
-      <c r="H166" s="3" t="n"/>
-      <c r="I166" s="3" t="n"/>
-      <c r="J166" s="3" t="n"/>
-      <c r="K166" s="3" t="n"/>
-      <c r="L166" s="3" t="n"/>
-      <c r="M166" s="3" t="n"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0165</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>서비스 회복 과정에서 직원이 고객을 정중하고 진심 어린 태도로 대했는지에 대해 고객이 느끼는 공정성은?</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>상호작용 공정성</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>분배 공정성</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>절차 공정성</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>결과 공정성</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>서비스 회복의 공정성은 보상 결과(분배), 처리 과정·속도(절차), 직원의 태도·예의(상호작용)로 나뉜다. 직원의 태도는 상호작용 공정성이다.</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>보상 결과나 처리 절차가 아니라 응대하는 사람의 예의에 관한 공정성입니다.</t>
+        </is>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N166" s="3" t="n"/>
-      <c r="O166" s="3" t="n"/>
-      <c r="P166" s="3" t="n"/>
-      <c r="Q166" s="3" t="n"/>
+      <c r="O166" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P166" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q166" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 서비스 마케팅 이론(서비스 회복 공정성 3차원), 교통안전공단 교재 직접 수록 여부 미확인 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n"/>
-      <c r="B167" s="3" t="n"/>
-      <c r="C167" s="3" t="n"/>
-      <c r="D167" s="3" t="n"/>
-      <c r="E167" s="3" t="n"/>
-      <c r="F167" s="3" t="n"/>
-      <c r="G167" s="3" t="n"/>
-      <c r="H167" s="3" t="n"/>
-      <c r="I167" s="3" t="n"/>
-      <c r="J167" s="3" t="n"/>
-      <c r="K167" s="3" t="n"/>
-      <c r="L167" s="3" t="n"/>
-      <c r="M167" s="3" t="n"/>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0166</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>서비스 실패가 일어났을 때 회복 노력에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>고객이 다시 항의할 때까지 기다리는 것이 좋다</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>원인이 완전히 밝혀질 때까지 고객에게 알리지 않는다</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>현장 직원은 어떤 경우에도 스스로 조치하지 않는다</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>실패를 알게 된 즉시 빨리 대응할수록 불만이 커지는 것을 막을 수 있다</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>서비스 회복은 신속성이 핵심이며, 늦어질수록 불만이 커지고 회복 비용도 늘어난다.</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>불은 작을 때 끄는 것이 쉽습니다.</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N167" s="3" t="n"/>
-      <c r="O167" s="3" t="n"/>
-      <c r="P167" s="3" t="n"/>
-      <c r="Q167" s="3" t="n"/>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q167" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n"/>
-      <c r="B168" s="3" t="n"/>
-      <c r="C168" s="3" t="n"/>
-      <c r="D168" s="3" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="n"/>
-      <c r="J168" s="3" t="n"/>
-      <c r="K168" s="3" t="n"/>
-      <c r="L168" s="3" t="n"/>
-      <c r="M168" s="3" t="n"/>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0167</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>고객의 말을 들을 때의 태도로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>고개를 끄덕이며 적절히 맞장구를 친다</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>중요한 내용은 메모하며 듣는다</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>고객 쪽으로 몸을 향하고 눈을 맞춘다</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>고객의 말이 끝나기 전에 짐작하여 말을 가로챈다</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>말을 가로채면 고객은 무시당한다고 느끼므로 끝까지 듣는 것이 경청의 기본이다.</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>경청은 '끝까지'가 핵심입니다.</t>
+        </is>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N168" s="3" t="n"/>
-      <c r="O168" s="3" t="n"/>
-      <c r="P168" s="3" t="n"/>
-      <c r="Q168" s="3" t="n"/>
+      <c r="O168" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q168" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n"/>
-      <c r="B169" s="3" t="n"/>
-      <c r="C169" s="3" t="n"/>
-      <c r="D169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="3" t="n"/>
-      <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="n"/>
-      <c r="J169" s="3" t="n"/>
-      <c r="K169" s="3" t="n"/>
-      <c r="L169" s="3" t="n"/>
-      <c r="M169" s="3" t="n"/>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0168</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>고객이 배송 주소와 희망 시간을 말했을 때 바람직한 경청 방법은?</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>기억에 의존하고 따로 확인하지 않는다</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>대충 들은 뒤 나중에 다시 전화해서 묻는다</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>중요한 내용을 되풀이해 말하며 맞게 이해했는지 확인한다</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>고객이 말하는 동안 다른 업무를 함께 처리한다</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>주소·시간처럼 틀리면 안 되는 정보는 복창하여 확인해야 배송 착오를 막을 수 있다.</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>들은 것을 다시 입으로 말해 보는 방법입니다.</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N169" s="3" t="n"/>
-      <c r="O169" s="3" t="n"/>
-      <c r="P169" s="3" t="n"/>
-      <c r="Q169" s="3" t="n"/>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P169" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q169" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n"/>
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
-      <c r="D170" s="3" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
-      <c r="H170" s="3" t="n"/>
-      <c r="I170" s="3" t="n"/>
-      <c r="J170" s="3" t="n"/>
-      <c r="K170" s="3" t="n"/>
-      <c r="L170" s="3" t="n"/>
-      <c r="M170" s="3" t="n"/>
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0169</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>표정에 대한 설명으로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>밝은 표정은 좋은 첫인상을 만든다</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>표정은 말보다 먼저 감정을 전달한다</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>피곤한 날에는 무표정해도 고객이 이해해 준다</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>사과할 때는 진지한 표정이 어울린다</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>고객은 직원의 사정을 알지 못하므로 컨디션과 관계없이 밝고 상황에 맞는 표정을 유지해야 한다.</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>고객은 직원의 사정을 알 수 없다는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N170" s="3" t="n"/>
-      <c r="O170" s="3" t="n"/>
-      <c r="P170" s="3" t="n"/>
-      <c r="Q170" s="3" t="n"/>
+      <c r="O170" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P170" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q170" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n"/>
-      <c r="B171" s="3" t="n"/>
-      <c r="C171" s="3" t="n"/>
-      <c r="D171" s="3" t="n"/>
-      <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n"/>
-      <c r="G171" s="3" t="n"/>
-      <c r="H171" s="3" t="n"/>
-      <c r="I171" s="3" t="n"/>
-      <c r="J171" s="3" t="n"/>
-      <c r="K171" s="3" t="n"/>
-      <c r="L171" s="3" t="n"/>
-      <c r="M171" s="3" t="n"/>
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0170</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>호칭 사용에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>친근감을 위해 처음 만난 고객을 '삼촌', '이모'라고 부른다</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>나이가 어려 보이는 고객에게도 '고객님'처럼 존중하는 호칭을 쓴다</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>나이가 어려 보이면 반말로 부른다</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>이름을 모르면 '저기요', '어이'라고 부른다</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>호칭은 고객의 나이나 외모와 관계없이 존중을 담아 일관되게 사용해야 한다.</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>나이와 외모는 호칭을 바꾸는 기준이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N171" s="3" t="n"/>
-      <c r="O171" s="3" t="n"/>
-      <c r="P171" s="3" t="n"/>
-      <c r="Q171" s="3" t="n"/>
+      <c r="O171" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P171" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q171" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n"/>
-      <c r="B172" s="3" t="n"/>
-      <c r="C172" s="3" t="n"/>
-      <c r="D172" s="3" t="n"/>
-      <c r="E172" s="3" t="n"/>
-      <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="n"/>
-      <c r="H172" s="3" t="n"/>
-      <c r="I172" s="3" t="n"/>
-      <c r="J172" s="3" t="n"/>
-      <c r="K172" s="3" t="n"/>
-      <c r="L172" s="3" t="n"/>
-      <c r="M172" s="3" t="n"/>
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0171</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>고객에게 쓰는 높임 표현 중 바르지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>주문하신 물건이 도착하셨습니다</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>주문하신 물건이 도착했습니다</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>잠시만 기다려 주시겠습니까</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>성함을 여쭤봐도 되겠습니까</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>높임의 대상은 사람이므로 물건에 '-시-'를 붙이는 것은 잘못된 사물 존칭이다.</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
+        <is>
+          <t>높여야 할 대상이 사람인지 물건인지 보세요.</t>
+        </is>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N172" s="3" t="n"/>
-      <c r="O172" s="3" t="n"/>
-      <c r="P172" s="3" t="n"/>
-      <c r="Q172" s="3" t="n"/>
+      <c r="O172" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P172" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q172" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 국립국어원 표준 언어 예절(사물 존대 오류) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n"/>
-      <c r="B173" s="3" t="n"/>
-      <c r="C173" s="3" t="n"/>
-      <c r="D173" s="3" t="n"/>
-      <c r="E173" s="3" t="n"/>
-      <c r="F173" s="3" t="n"/>
-      <c r="G173" s="3" t="n"/>
-      <c r="H173" s="3" t="n"/>
-      <c r="I173" s="3" t="n"/>
-      <c r="J173" s="3" t="n"/>
-      <c r="K173" s="3" t="n"/>
-      <c r="L173" s="3" t="n"/>
-      <c r="M173" s="3" t="n"/>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0172</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>'죄송합니다만', '실례지만', '번거로우시겠지만'처럼 부탁이나 거절의 말 앞에 붙여 부드럽게 전달하는 표현은?</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>은어</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>쿠션 언어</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>전문 용어</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>명령형 언어</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>쿠션 언어는 충격을 줄여 주는 완충 표현으로, 부탁·거절할 때 고객의 거부감을 줄여 준다.</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>딱딱한 말이 부딪치기 전에 충격을 덜어 주는 역할을 하는 표현입니다.</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N173" s="3" t="n"/>
-      <c r="O173" s="3" t="n"/>
-      <c r="P173" s="3" t="n"/>
-      <c r="Q173" s="3" t="n"/>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P173" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n"/>
-      <c r="B174" s="3" t="n"/>
-      <c r="C174" s="3" t="n"/>
-      <c r="D174" s="3" t="n"/>
-      <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n"/>
-      <c r="G174" s="3" t="n"/>
-      <c r="H174" s="3" t="n"/>
-      <c r="I174" s="3" t="n"/>
-      <c r="J174" s="3" t="n"/>
-      <c r="K174" s="3" t="n"/>
-      <c r="L174" s="3" t="n"/>
-      <c r="M174" s="3" t="n"/>
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0173</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>고객의 요청을 바로 들어줄 수 없을 때 바람직한 표현은?</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>안 됩니다. 규정이에요</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>그건 불가능하니 다른 데 알아보세요</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>오늘은 어렵지만 내일 오전에는 배송해 드릴 수 있습니다</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>왜 그런 걸 요청하시는지 모르겠네요</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>거절할 때도 '안 된다'로 끝내지 않고 가능한 대안을 긍정적으로 제시하는 것이 바람직하다.</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="inlineStr">
+        <is>
+          <t>'할 수 없는 것'보다 '할 수 있는 것'을 말해 보세요.</t>
+        </is>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N174" s="3" t="n"/>
-      <c r="O174" s="3" t="n"/>
-      <c r="P174" s="3" t="n"/>
-      <c r="Q174" s="3" t="n"/>
+      <c r="O174" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P174" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q174" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n"/>
-      <c r="B175" s="3" t="n"/>
-      <c r="C175" s="3" t="n"/>
-      <c r="D175" s="3" t="n"/>
-      <c r="E175" s="3" t="n"/>
-      <c r="F175" s="3" t="n"/>
-      <c r="G175" s="3" t="n"/>
-      <c r="H175" s="3" t="n"/>
-      <c r="I175" s="3" t="n"/>
-      <c r="J175" s="3" t="n"/>
-      <c r="K175" s="3" t="n"/>
-      <c r="L175" s="3" t="n"/>
-      <c r="M175" s="3" t="n"/>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0174</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>의사소통에서 상대에게 주는 인상은 말의 내용보다 표정·태도 같은 시각 요소와 목소리 같은 청각 요소의 영향이 더 크다는 연구로 널리 알려진 법칙은?</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>메라비언의 법칙</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>파레토 법칙</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>하인리히 법칙</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>머피의 법칙</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>메라비언의 법칙은 인상 형성에서 말의 내용보다 시각·청각 요소의 비중이 크다는 연구 결과로, 서비스 교육에서 널리 쓰인다.</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>말의 내용, 목소리, 표정·태도가 인상에 미치는 비중을 비교한 연구입니다.</t>
+        </is>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N175" s="3" t="n"/>
-      <c r="O175" s="3" t="n"/>
-      <c r="P175" s="3" t="n"/>
-      <c r="Q175" s="3" t="n"/>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P175" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q175" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 커뮤니케이션 일반 이론(Mehrabian, 1971), 교통안전공단 교재 직접 수록 여부 미확인 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n"/>
-      <c r="B176" s="3" t="n"/>
-      <c r="C176" s="3" t="n"/>
-      <c r="D176" s="3" t="n"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="3" t="n"/>
-      <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="n"/>
-      <c r="J176" s="3" t="n"/>
-      <c r="K176" s="3" t="n"/>
-      <c r="L176" s="3" t="n"/>
-      <c r="M176" s="3" t="n"/>
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0175</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>고객 전화를 받을 때의 바른 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>고객이 끊을 때까지 벨이 여러 번 울려도 기다린다</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>벨이 울리면 되도록 세 번 이내에 받는다</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>통화 중에 옆 사람과 대화하며 응대한다</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>바쁠 때는 받자마자 용건만 묻고 끊는다</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>전화는 빨리 받는 것이 기본 예절이며, 늦게 받았다면 기다리게 한 데 대해 사과한다.</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>고객을 오래 기다리게 하지 않는 것이 기본입니다.</t>
+        </is>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N176" s="3" t="n"/>
-      <c r="O176" s="3" t="n"/>
-      <c r="P176" s="3" t="n"/>
-      <c r="Q176" s="3" t="n"/>
+      <c r="O176" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q176" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n"/>
-      <c r="B177" s="3" t="n"/>
-      <c r="C177" s="3" t="n"/>
-      <c r="D177" s="3" t="n"/>
-      <c r="E177" s="3" t="n"/>
-      <c r="F177" s="3" t="n"/>
-      <c r="G177" s="3" t="n"/>
-      <c r="H177" s="3" t="n"/>
-      <c r="I177" s="3" t="n"/>
-      <c r="J177" s="3" t="n"/>
-      <c r="K177" s="3" t="n"/>
-      <c r="L177" s="3" t="n"/>
-      <c r="M177" s="3" t="n"/>
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0176</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>자리에 없는 동료를 찾는 전화를 대신 받았을 때 바른 응대는?</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>동료의 휴대전화 번호와 개인 일정을 자세히 알려 준다</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>모른다고 말하고 바로 끊는다</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>메모 없이 나중에 기억나면 전한다</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>부재 사유를 간단히 알리고 용건과 연락처를 메모하여 전달한다</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H177" s="3" t="inlineStr">
+        <is>
+          <t>대신 받은 전화는 부재를 알리고 용건을 정확히 메모해 전달하되, 동료의 개인정보는 함부로 알려 주지 않는다.</t>
+        </is>
+      </c>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>정확한 전달과 개인정보 보호를 함께 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N177" s="3" t="n"/>
-      <c r="O177" s="3" t="n"/>
-      <c r="P177" s="3" t="n"/>
-      <c r="Q177" s="3" t="n"/>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P177" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q177" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n"/>
-      <c r="B178" s="3" t="n"/>
-      <c r="C178" s="3" t="n"/>
-      <c r="D178" s="3" t="n"/>
-      <c r="E178" s="3" t="n"/>
-      <c r="F178" s="3" t="n"/>
-      <c r="G178" s="3" t="n"/>
-      <c r="H178" s="3" t="n"/>
-      <c r="I178" s="3" t="n"/>
-      <c r="J178" s="3" t="n"/>
-      <c r="K178" s="3" t="n"/>
-      <c r="L178" s="3" t="n"/>
-      <c r="M178" s="3" t="n"/>
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0177</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>통화 중 확인할 일이 있어 고객을 잠시 기다리게 해야 할 때 바른 방법은?</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>기다리는 이유를 알리고 양해를 구하며, 오래 걸리면 다시 걸겠다고 안내한다</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>아무 말 없이 수화기를 내려놓고 확인하러 간다</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>확인이 끝날 때까지 몇 분이 걸려도 그대로 기다리게 한다</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>다른 직원에게 말없이 전화를 돌린다</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>고객은 이유를 모른 채 기다릴 때 더 불편을 느끼므로 이유를 설명하고, 오래 걸리면 다시 연락하는 것이 예절이다.</t>
+        </is>
+      </c>
+      <c r="I178" s="3" t="inlineStr">
+        <is>
+          <t>기다림이 길 때 고객에게 줄 수 있는 다른 선택을 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N178" s="3" t="n"/>
-      <c r="O178" s="3" t="n"/>
-      <c r="P178" s="3" t="n"/>
-      <c r="Q178" s="3" t="n"/>
+      <c r="O178" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q178" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n"/>
-      <c r="B179" s="3" t="n"/>
-      <c r="C179" s="3" t="n"/>
-      <c r="D179" s="3" t="n"/>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="3" t="n"/>
-      <c r="H179" s="3" t="n"/>
-      <c r="I179" s="3" t="n"/>
-      <c r="J179" s="3" t="n"/>
-      <c r="K179" s="3" t="n"/>
-      <c r="L179" s="3" t="n"/>
-      <c r="M179" s="3" t="n"/>
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0178</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>고객에게 배송 안내 문자를 보낼 때 바람직한 것은?</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>늦은 밤이나 새벽에도 생각날 때 바로 보낸다</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>줄임말과 이모티콘을 많이 섞어 친근하게 쓴다</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>회사와 담당자 이름, 도착 예정 시간을 분명히 적어 보낸다</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>누가 보냈는지 적지 않고 '곧 도착'만 보낸다</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" s="3" t="inlineStr">
+        <is>
+          <t>배송 문자는 누가, 언제 오는지 분명해야 고객이 믿고 준비할 수 있으며, 늦은 시간 발송은 피한다.</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr">
+        <is>
+          <t>받는 사람이 '누가, 언제'를 바로 알 수 있어야 합니다.</t>
+        </is>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N179" s="3" t="n"/>
-      <c r="O179" s="3" t="n"/>
-      <c r="P179" s="3" t="n"/>
-      <c r="Q179" s="3" t="n"/>
+      <c r="O179" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q179" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n"/>
-      <c r="B180" s="3" t="n"/>
-      <c r="C180" s="3" t="n"/>
-      <c r="D180" s="3" t="n"/>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
-      <c r="G180" s="3" t="n"/>
-      <c r="H180" s="3" t="n"/>
-      <c r="I180" s="3" t="n"/>
-      <c r="J180" s="3" t="n"/>
-      <c r="K180" s="3" t="n"/>
-      <c r="L180" s="3" t="n"/>
-      <c r="M180" s="3" t="n"/>
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0179</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>화물차 운행 중 고객의 전화가 계속 걸려 올 때 바람직한 대처는?</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>속도를 줄이고 휴대전화를 손에 든 채 받는다</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>신호 대기 중에 문자로 길게 답장한다</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>안전한 곳에 차를 세운 뒤 통화하거나 다시 전화한다</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>중요한 고객이므로 차로를 바꾸면서 바로 받는다</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>고객 응대보다 안전이 우선이므로 안전한 곳에 정차한 뒤 통화하는 것이 바람직하다.</t>
+        </is>
+      </c>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>고객 응대와 안전 중 무엇이 먼저인지 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N180" s="3" t="n"/>
-      <c r="O180" s="3" t="n"/>
-      <c r="P180" s="3" t="n"/>
-      <c r="Q180" s="3" t="n"/>
+      <c r="O180" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P180" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q180" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n"/>
-      <c r="B181" s="3" t="n"/>
-      <c r="C181" s="3" t="n"/>
-      <c r="D181" s="3" t="n"/>
-      <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="n"/>
-      <c r="G181" s="3" t="n"/>
-      <c r="H181" s="3" t="n"/>
-      <c r="I181" s="3" t="n"/>
-      <c r="J181" s="3" t="n"/>
-      <c r="K181" s="3" t="n"/>
-      <c r="L181" s="3" t="n"/>
-      <c r="M181" s="3" t="n"/>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0180</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>고객에게 먼저 전화를 걸 때의 바른 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>소속과 이름을 밝히고 통화가 괜찮은지 확인한 뒤 용건을 말한다</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>인사 없이 바로 용건부터 말한다</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>상대가 누군지 확인하지 않고 용건을 길게 설명한다</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>통화 가능 여부와 관계없이 용건을 끝까지 말한다</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>전화를 건 쪽은 먼저 자신을 밝히고 상대의 형편을 확인한 뒤 용건을 간단명료하게 전한다.</t>
+        </is>
+      </c>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>상대가 지금 통화하기 좋은 상황인지부터 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N181" s="3" t="n"/>
-      <c r="O181" s="3" t="n"/>
-      <c r="P181" s="3" t="n"/>
-      <c r="Q181" s="3" t="n"/>
+      <c r="O181" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P181" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q181" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n"/>
-      <c r="B182" s="3" t="n"/>
-      <c r="C182" s="3" t="n"/>
-      <c r="D182" s="3" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="3" t="n"/>
-      <c r="H182" s="3" t="n"/>
-      <c r="I182" s="3" t="n"/>
-      <c r="J182" s="3" t="n"/>
-      <c r="K182" s="3" t="n"/>
-      <c r="L182" s="3" t="n"/>
-      <c r="M182" s="3" t="n"/>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0181</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자의 흡연 예절로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>창문을 열어 두면 고객이 탄 차 안에서도 피워도 된다</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>배송 대기 중에는 고객 집 앞에서 피워도 된다</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>담배꽁초는 정해진 장소에 버리고 창밖으로 던지지 않는다</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>휴게소에서는 장소를 가리지 않고 피워도 된다</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>꽁초 투기는 화재와 환경오염의 원인이 되고 회사 이미지도 떨어뜨리므로 정해진 장소에서만 처리한다.</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>불씨와 쓰레기가 어디로 가는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N182" s="3" t="n"/>
-      <c r="O182" s="3" t="n"/>
-      <c r="P182" s="3" t="n"/>
-      <c r="Q182" s="3" t="n"/>
+      <c r="O182" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q182" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n"/>
-      <c r="B183" s="3" t="n"/>
-      <c r="C183" s="3" t="n"/>
-      <c r="D183" s="3" t="n"/>
-      <c r="E183" s="3" t="n"/>
-      <c r="F183" s="3" t="n"/>
-      <c r="G183" s="3" t="n"/>
-      <c r="H183" s="3" t="n"/>
-      <c r="I183" s="3" t="n"/>
-      <c r="J183" s="3" t="n"/>
-      <c r="K183" s="3" t="n"/>
-      <c r="L183" s="3" t="n"/>
-      <c r="M183" s="3" t="n"/>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0182</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>장시간 운전하는 운전자가 휴식할 때 하면 좋은 건강 관리로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>휴식 시간에도 차 안에 앉아 휴대전화만 본다</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>휴식 시간을 줄여 그만큼 일찍 출발한다</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>에너지 음료를 여러 캔 마셔 피로를 버틴다</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>차에서 내려 가벼운 체조와 스트레칭으로 굳은 근육을 풀어 준다</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>오래 앉아 있으면 혈액순환이 나빠지고 근육이 굳으므로 휴식 때 몸을 움직여 피로를 푸는 것이 좋다.</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>오래 같은 자세로 있던 몸에 필요한 것을 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N183" s="3" t="n"/>
-      <c r="O183" s="3" t="n"/>
-      <c r="P183" s="3" t="n"/>
-      <c r="Q183" s="3" t="n"/>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="3" t="n"/>
-      <c r="C184" s="3" t="n"/>
-      <c r="D184" s="3" t="n"/>
-      <c r="E184" s="3" t="n"/>
-      <c r="F184" s="3" t="n"/>
-      <c r="G184" s="3" t="n"/>
-      <c r="H184" s="3" t="n"/>
-      <c r="I184" s="3" t="n"/>
-      <c r="J184" s="3" t="n"/>
-      <c r="K184" s="3" t="n"/>
-      <c r="L184" s="3" t="n"/>
-      <c r="M184" s="3" t="n"/>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0183</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>직업 운전자의 식사 습관으로 바람직한 것은?</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>끼니를 거르지 않고 규칙적으로 먹되 운행 직전의 과식은 피한다</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>시간을 아끼기 위해 하루 한 끼만 몰아서 먹는다</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>운전 중 졸리지 않도록 운행 직전에 배부르게 먹는다</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>식사 대신 커피와 과자로 운행 내내 버틴다</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>불규칙한 식사는 건강을 해치고, 과식은 식곤증으로 졸음운전을 부를 수 있다.</t>
+        </is>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>배가 너무 고파도, 너무 불러도 운전에 좋지 않습니다.</t>
+        </is>
+      </c>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N184" s="3" t="n"/>
-      <c r="O184" s="3" t="n"/>
-      <c r="P184" s="3" t="n"/>
-      <c r="Q184" s="3" t="n"/>
+      <c r="O184" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q184" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n"/>
-      <c r="B185" s="3" t="n"/>
-      <c r="C185" s="3" t="n"/>
-      <c r="D185" s="3" t="n"/>
-      <c r="E185" s="3" t="n"/>
-      <c r="F185" s="3" t="n"/>
-      <c r="G185" s="3" t="n"/>
-      <c r="H185" s="3" t="n"/>
-      <c r="I185" s="3" t="n"/>
-      <c r="J185" s="3" t="n"/>
-      <c r="K185" s="3" t="n"/>
-      <c r="L185" s="3" t="n"/>
-      <c r="M185" s="3" t="n"/>
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0184</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>고혈압·당뇨 같은 만성질환이 있는 직업 운전자의 관리로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>증상이 없으면 약을 마음대로 끊는다</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>정기 검진을 받고 처방약을 꾸준히 먹으며, 몸 상태가 나쁘면 운행을 미룬다</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>운행에 방해되므로 검진은 받지 않는다</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>어지러워도 일정이 급하면 그대로 운행한다</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>만성질환은 운전 중 갑작스러운 발작·의식 저하로 이어질 수 있어 꾸준한 관리와 컨디션 점검이 필요하다.</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>'증상이 없다'와 '병이 없다'는 다릅니다.</t>
+        </is>
+      </c>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N185" s="3" t="n"/>
-      <c r="O185" s="3" t="n"/>
-      <c r="P185" s="3" t="n"/>
-      <c r="Q185" s="3" t="n"/>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 운송서비스 교재(직업윤리·고객응대) 일반 내용, 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n"/>
-      <c r="B186" s="3" t="n"/>
-      <c r="C186" s="3" t="n"/>
-      <c r="D186" s="3" t="n"/>
-      <c r="E186" s="3" t="n"/>
-      <c r="F186" s="3" t="n"/>
-      <c r="G186" s="3" t="n"/>
-      <c r="H186" s="3" t="n"/>
-      <c r="I186" s="3" t="n"/>
-      <c r="J186" s="3" t="n"/>
-      <c r="K186" s="3" t="n"/>
-      <c r="L186" s="3" t="n"/>
-      <c r="M186" s="3" t="n"/>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0185</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>물류 관리의 목표로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>물류비와 관계없이 재고를 최대한 많이 갖는 것</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>고객서비스를 낮추어서라도 운송비만 줄이는 것</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>운송 수단을 한 가지로만 통일하는 것</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>물류비를 줄이면서 고객서비스 수준을 높이는 것</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>물류 관리는 비용 절감과 고객서비스 향상이라는 두 목표를 균형 있게 달성하는 것을 목표로 한다.</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>한쪽만이 아니라 두 가지를 함께 추구합니다.</t>
+        </is>
+      </c>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N186" s="3" t="n"/>
-      <c r="O186" s="3" t="n"/>
-      <c r="P186" s="3" t="n"/>
-      <c r="Q186" s="3" t="n"/>
+      <c r="O186" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n"/>
-      <c r="B187" s="3" t="n"/>
-      <c r="C187" s="3" t="n"/>
-      <c r="D187" s="3" t="n"/>
-      <c r="E187" s="3" t="n"/>
-      <c r="F187" s="3" t="n"/>
-      <c r="G187" s="3" t="n"/>
-      <c r="H187" s="3" t="n"/>
-      <c r="I187" s="3" t="n"/>
-      <c r="J187" s="3" t="n"/>
-      <c r="K187" s="3" t="n"/>
-      <c r="L187" s="3" t="n"/>
-      <c r="M187" s="3" t="n"/>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0186</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>완제품을 물류센터에서 소매점이나 소비자에게 전달하는 단계의 물류는?</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>조달물류</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>판매물류</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>생산물류</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>폐기물류</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>판매물류는 완제품이 출하되어 고객에게 전달되기까지의 물류로, 수배송·배송센터 운영 등이 포함된다.</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>상품이 '팔려 나가는' 단계를 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N187" s="3" t="n"/>
-      <c r="O187" s="3" t="n"/>
-      <c r="P187" s="3" t="n"/>
-      <c r="Q187" s="3" t="n"/>
+      <c r="O187" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n"/>
-      <c r="B188" s="3" t="n"/>
-      <c r="C188" s="3" t="n"/>
-      <c r="D188" s="3" t="n"/>
-      <c r="E188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="3" t="n"/>
-      <c r="H188" s="3" t="n"/>
-      <c r="I188" s="3" t="n"/>
-      <c r="J188" s="3" t="n"/>
-      <c r="K188" s="3" t="n"/>
-      <c r="L188" s="3" t="n"/>
-      <c r="M188" s="3" t="n"/>
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0187</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>더 이상 쓸 수 없게 된 제품이나 포장재를 처분하기 위해 운송·처리하는 물류는?</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>폐기물류</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>판매물류</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>조달물류</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>생산물류</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>폐기물류는 가치를 잃은 제품·포장재 등을 처분하는 과정의 물류이다.</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>물자가 일생을 마치는 마지막 단계입니다.</t>
+        </is>
+      </c>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N188" s="3" t="n"/>
-      <c r="O188" s="3" t="n"/>
-      <c r="P188" s="3" t="n"/>
-      <c r="Q188" s="3" t="n"/>
+      <c r="O188" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q188" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n"/>
-      <c r="B189" s="3" t="n"/>
-      <c r="C189" s="3" t="n"/>
-      <c r="D189" s="3" t="n"/>
-      <c r="E189" s="3" t="n"/>
-      <c r="F189" s="3" t="n"/>
-      <c r="G189" s="3" t="n"/>
-      <c r="H189" s="3" t="n"/>
-      <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
-      <c r="K189" s="3" t="n"/>
-      <c r="L189" s="3" t="n"/>
-      <c r="M189" s="3" t="n"/>
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0188</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>물류 활동 영역을 물자의 흐름 순서대로 바르게 나열한 것은?</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>생산물류 → 조달물류 → 판매물류 → 회수·폐기물류</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>판매물류 → 조달물류 → 생산물류 → 회수·폐기물류</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>조달물류 → 생산물류 → 판매물류 → 회수·폐기물류</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>조달물류 → 판매물류 → 생산물류 → 회수·폐기물류</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>원자재를 들여오고(조달), 만들고(생산), 팔고(판매), 되돌리거나 버리는(회수·폐기) 순서로 이어진다.</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>원자재가 공장에 들어오는 것부터 시작합니다.</t>
+        </is>
+      </c>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N189" s="3" t="n"/>
-      <c r="O189" s="3" t="n"/>
-      <c r="P189" s="3" t="n"/>
-      <c r="Q189" s="3" t="n"/>
+      <c r="O189" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P189" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q189" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n"/>
-      <c r="B190" s="3" t="n"/>
-      <c r="C190" s="3" t="n"/>
-      <c r="D190" s="3" t="n"/>
-      <c r="E190" s="3" t="n"/>
-      <c r="F190" s="3" t="n"/>
-      <c r="G190" s="3" t="n"/>
-      <c r="H190" s="3" t="n"/>
-      <c r="I190" s="3" t="n"/>
-      <c r="J190" s="3" t="n"/>
-      <c r="K190" s="3" t="n"/>
-      <c r="L190" s="3" t="n"/>
-      <c r="M190" s="3" t="n"/>
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0189</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>물류정책기본법에서 정의하는 '물류'의 범위로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>재화를 만드는 제조 공정만을 말한다</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>재화가 조달·생산되어 수요자에게 전달되거나 소비자로부터 회수되어 폐기될 때까지의 운송·보관·하역 등</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>매매 계약으로 소유권이 옮겨 가는 거래만을 말한다</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>소비자에게 전달되는 순간까지만이며 회수·폐기는 포함하지 않는다</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>물류정책기본법은 조달·생산부터 회수·폐기까지의 운송·보관·하역과 이에 부가되는 가공·포장·정보통신 등을 물류로 정의한다.</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>시작은 조달, 끝은 생각보다 더 뒤에 있습니다.</t>
+        </is>
+      </c>
+      <c r="J190" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N190" s="3" t="n"/>
-      <c r="O190" s="3" t="n"/>
-      <c r="P190" s="3" t="n"/>
-      <c r="Q190" s="3" t="n"/>
+      <c r="O190" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q190" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 물류정책기본법 제2조 제1항 제1호(물류의 정의), law.go.kr</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n"/>
-      <c r="B191" s="3" t="n"/>
-      <c r="C191" s="3" t="n"/>
-      <c r="D191" s="3" t="n"/>
-      <c r="E191" s="3" t="n"/>
-      <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="n"/>
-      <c r="H191" s="3" t="n"/>
-      <c r="I191" s="3" t="n"/>
-      <c r="J191" s="3" t="n"/>
-      <c r="K191" s="3" t="n"/>
-      <c r="L191" s="3" t="n"/>
-      <c r="M191" s="3" t="n"/>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0190</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>물류 표준화의 효과로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>하역·운송의 기계화가 쉬워진다</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>기업마다 다른 규격을 써서 서로 호환이 어려워진다</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>물류비를 줄일 수 있다</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>기업 간 공동 물류가 쉬워진다</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>물류 표준화는 규격을 통일해 호환성을 높이는 것이 목적이므로 호환이 어려워지는 것은 효과가 아니다.</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
+          <t>'표준'이라는 말의 반대 상황을 찾으세요.</t>
+        </is>
+      </c>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N191" s="3" t="n"/>
-      <c r="O191" s="3" t="n"/>
-      <c r="P191" s="3" t="n"/>
-      <c r="Q191" s="3" t="n"/>
+      <c r="O191" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q191" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n"/>
-      <c r="B192" s="3" t="n"/>
-      <c r="C192" s="3" t="n"/>
-      <c r="D192" s="3" t="n"/>
-      <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
-      <c r="H192" s="3" t="n"/>
-      <c r="I192" s="3" t="n"/>
-      <c r="J192" s="3" t="n"/>
-      <c r="K192" s="3" t="n"/>
-      <c r="L192" s="3" t="n"/>
-      <c r="M192" s="3" t="n"/>
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0191</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>포장 치수를 파렛트·컨테이너·차량 적재함 치수와 배수 또는 분할 관계가 되도록 맞추는 것은?</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>물류 모듈화</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>모달 시프트</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>밀크런</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>물류 모듈화는 기준 치수를 정해 포장·파렛트·적재함 치수를 서로 딱 맞게 하여 적재 효율을 높이는 것이다.</t>
+        </is>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>레고 블록처럼 기준 단위에 맞춰 크기를 맞추는 개념입니다.</t>
+        </is>
+      </c>
+      <c r="J192" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N192" s="3" t="n"/>
-      <c r="O192" s="3" t="n"/>
-      <c r="P192" s="3" t="n"/>
-      <c r="Q192" s="3" t="n"/>
+      <c r="O192" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q192" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n"/>
-      <c r="B193" s="3" t="n"/>
-      <c r="C193" s="3" t="n"/>
-      <c r="D193" s="3" t="n"/>
-      <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="3" t="n"/>
-      <c r="H193" s="3" t="n"/>
-      <c r="I193" s="3" t="n"/>
-      <c r="J193" s="3" t="n"/>
-      <c r="K193" s="3" t="n"/>
-      <c r="L193" s="3" t="n"/>
-      <c r="M193" s="3" t="n"/>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0192</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>여러 기업이 표준 파렛트를 공동으로 이용하고 회수·관리하는 체계는?</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>VMI</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>루트 배송</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>파렛트 풀 시스템</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>파렛트 풀 시스템은 표준 파렛트를 함께 쓰고 관리해 빈 파렛트 회수 부담과 비용을 줄이는 제도이다.</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>회사마다 따로 갖지 않고 한데 모아 돌려 쓰는 방식을 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J193" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N193" s="3" t="n"/>
-      <c r="O193" s="3" t="n"/>
-      <c r="P193" s="3" t="n"/>
-      <c r="Q193" s="3" t="n"/>
+      <c r="O193" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P193" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q193" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n"/>
-      <c r="B194" s="3" t="n"/>
-      <c r="C194" s="3" t="n"/>
-      <c r="D194" s="3" t="n"/>
-      <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="3" t="n"/>
-      <c r="H194" s="3" t="n"/>
-      <c r="I194" s="3" t="n"/>
-      <c r="J194" s="3" t="n"/>
-      <c r="K194" s="3" t="n"/>
-      <c r="L194" s="3" t="n"/>
-      <c r="M194" s="3" t="n"/>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0193</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>다른 사람의 물건을 맡아 보관해 주고 보관료를 받는 창고는?</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>자가창고</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>영업창고</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>보세창고</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>냉장창고</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>영업창고는 창고업자가 타인의 물품을 보관하고 보관료를 받는 창고이다.</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>창고 운영 자체가 돈벌이인 경우입니다.</t>
+        </is>
+      </c>
+      <c r="J194" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N194" s="3" t="n"/>
-      <c r="O194" s="3" t="n"/>
-      <c r="P194" s="3" t="n"/>
-      <c r="Q194" s="3" t="n"/>
+      <c r="O194" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q194" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n"/>
-      <c r="B195" s="3" t="n"/>
-      <c r="C195" s="3" t="n"/>
-      <c r="D195" s="3" t="n"/>
-      <c r="E195" s="3" t="n"/>
-      <c r="F195" s="3" t="n"/>
-      <c r="G195" s="3" t="n"/>
-      <c r="H195" s="3" t="n"/>
-      <c r="I195" s="3" t="n"/>
-      <c r="J195" s="3" t="n"/>
-      <c r="K195" s="3" t="n"/>
-      <c r="L195" s="3" t="n"/>
-      <c r="M195" s="3" t="n"/>
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0194</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>수입 화물을 관세 등을 내기 전 상태로 보관할 수 있도록 세관의 특허를 받은 창고는?</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>영업창고</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>자가창고</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>유통창고</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>보세창고</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>보세창고는 세관장의 특허를 받아 외국 물품을 관세 미납 상태로 보관할 수 있는 창고이다.</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>세관의 특허를 받아 외국 물품을 통관 전 상태로 두는 곳입니다.</t>
+        </is>
+      </c>
+      <c r="J195" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N195" s="3" t="n"/>
-      <c r="O195" s="3" t="n"/>
-      <c r="P195" s="3" t="n"/>
-      <c r="Q195" s="3" t="n"/>
+      <c r="O195" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q195" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 관세법상 보세구역(특허보세구역) 일반 내용, 조문 미대조 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n"/>
-      <c r="B196" s="3" t="n"/>
-      <c r="C196" s="3" t="n"/>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
-      <c r="H196" s="3" t="n"/>
-      <c r="I196" s="3" t="n"/>
-      <c r="J196" s="3" t="n"/>
-      <c r="K196" s="3" t="n"/>
-      <c r="L196" s="3" t="n"/>
-      <c r="M196" s="3" t="n"/>
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0195</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>자가창고의 장점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>초기 투자비가 들지 않는다</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>물량이 줄어도 고정비 부담이 없다</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>자기 회사 상품 특성에 맞게 설비를 갖추고 자유롭게 운영할 수 있다</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>필요할 때만 공간을 빌려 쓸 수 있다</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>자가창고는 직접 소유·운영하므로 맞춤 설비와 운영의 자유가 장점이지만, 투자비와 고정비 부담이 크다.</t>
+        </is>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>내 집을 가진 것의 좋은 점을 떠올리세요.</t>
+        </is>
+      </c>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N196" s="3" t="n"/>
-      <c r="O196" s="3" t="n"/>
-      <c r="P196" s="3" t="n"/>
-      <c r="Q196" s="3" t="n"/>
+      <c r="O196" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P196" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q196" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n"/>
-      <c r="B197" s="3" t="n"/>
-      <c r="C197" s="3" t="n"/>
-      <c r="D197" s="3" t="n"/>
-      <c r="E197" s="3" t="n"/>
-      <c r="F197" s="3" t="n"/>
-      <c r="G197" s="3" t="n"/>
-      <c r="H197" s="3" t="n"/>
-      <c r="I197" s="3" t="n"/>
-      <c r="J197" s="3" t="n"/>
-      <c r="K197" s="3" t="n"/>
-      <c r="L197" s="3" t="n"/>
-      <c r="M197" s="3" t="n"/>
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0196</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>단순 보관 위주의 창고와 비교한 물류센터(배송센터)의 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>화물을 오래 쌓아 두는 것만 목적으로 한다</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>보관뿐 아니라 분류·포장·유통가공·배송 등의 기능을 함께 수행한다</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>입고된 화물은 출고하지 않는다</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>고객 주문 정보와 관계없이 운영된다</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>물류센터는 보관 중심의 창고에서 발전해 주문 처리·분류·가공·배송까지 하는 흐름 중심 시설이다.</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>'쌓아 두는 곳'에서 '흘려보내는 곳'으로 바뀌었습니다.</t>
+        </is>
+      </c>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N197" s="3" t="n"/>
-      <c r="O197" s="3" t="n"/>
-      <c r="P197" s="3" t="n"/>
-      <c r="Q197" s="3" t="n"/>
+      <c r="O197" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P197" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q197" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n"/>
-      <c r="B198" s="3" t="n"/>
-      <c r="C198" s="3" t="n"/>
-      <c r="D198" s="3" t="n"/>
-      <c r="E198" s="3" t="n"/>
-      <c r="F198" s="3" t="n"/>
-      <c r="G198" s="3" t="n"/>
-      <c r="H198" s="3" t="n"/>
-      <c r="I198" s="3" t="n"/>
-      <c r="J198" s="3" t="n"/>
-      <c r="K198" s="3" t="n"/>
-      <c r="L198" s="3" t="n"/>
-      <c r="M198" s="3" t="n"/>
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0197</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>물류센터 입지를 정할 때 가장 중요하게 고려할 사항으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>주변 경치가 좋은지 여부</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>주요 고객과 도로망에 대한 접근성 및 수송 비용</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>대표의 집과 가까운지 여부</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>땅값이 가장 비싼 도심 한가운데인지 여부</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>물류센터는 화물이 드나드는 곳이므로 고객·도로망 접근성과 수송비가 입지 선정의 핵심이다.</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>화물차가 얼마나 쉽고 싸게 드나들 수 있는지 보세요.</t>
+        </is>
+      </c>
+      <c r="J198" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N198" s="3" t="n"/>
-      <c r="O198" s="3" t="n"/>
-      <c r="P198" s="3" t="n"/>
-      <c r="Q198" s="3" t="n"/>
+      <c r="O198" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q198" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n"/>
-      <c r="B199" s="3" t="n"/>
-      <c r="C199" s="3" t="n"/>
-      <c r="D199" s="3" t="n"/>
-      <c r="E199" s="3" t="n"/>
-      <c r="F199" s="3" t="n"/>
-      <c r="G199" s="3" t="n"/>
-      <c r="H199" s="3" t="n"/>
-      <c r="I199" s="3" t="n"/>
-      <c r="J199" s="3" t="n"/>
-      <c r="K199" s="3" t="n"/>
-      <c r="L199" s="3" t="n"/>
-      <c r="M199" s="3" t="n"/>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0198</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>물류센터에서 주문서에 따라 보관 장소에서 필요한 물품을 꺼내 모으는 작업은?</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>래핑</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>피킹</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>검수</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>적치</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>피킹은 주문 내용에 맞추어 보관 위치에서 물품을 골라 꺼내는 작업으로, 물류센터 작업 중 인력이 많이 드는 부분이다.</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>주문서를 들고 선반을 돌아다니는 작업을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N199" s="3" t="n"/>
-      <c r="O199" s="3" t="n"/>
-      <c r="P199" s="3" t="n"/>
-      <c r="Q199" s="3" t="n"/>
+      <c r="O199" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P199" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q199" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조 · 교차 점검 반영</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n"/>
-      <c r="B200" s="3" t="n"/>
-      <c r="C200" s="3" t="n"/>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
-      <c r="J200" s="3" t="n"/>
-      <c r="K200" s="3" t="n"/>
-      <c r="L200" s="3" t="n"/>
-      <c r="M200" s="3" t="n"/>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0199</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>최대적재량 5톤 화물차에 4톤의 화물을 실었을 때 적재율은?</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>125%</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>적재율은 실제 적재량을 최대적재량으로 나눈 비율이므로 4 ÷ 5 × 100 = 80%이다.</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>실제로 실은 양이 분자, 실을 수 있는 양이 분모입니다.</t>
+        </is>
+      </c>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N200" s="3" t="n"/>
-      <c r="O200" s="3" t="n"/>
-      <c r="P200" s="3" t="n"/>
-      <c r="Q200" s="3" t="n"/>
+      <c r="O200" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q200" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 적재율 정의(실제 적재량/최대적재량×100)에 따른 계산</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n"/>
-      <c r="B201" s="3" t="n"/>
-      <c r="C201" s="3" t="n"/>
-      <c r="D201" s="3" t="n"/>
-      <c r="E201" s="3" t="n"/>
-      <c r="F201" s="3" t="n"/>
-      <c r="G201" s="3" t="n"/>
-      <c r="H201" s="3" t="n"/>
-      <c r="I201" s="3" t="n"/>
-      <c r="J201" s="3" t="n"/>
-      <c r="K201" s="3" t="n"/>
-      <c r="L201" s="3" t="n"/>
-      <c r="M201" s="3" t="n"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>SERVICE-0200</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>차량 배차 계획을 세울 때 바람직한 것은?</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>화물이 적어도 항상 가장 큰 차를 보낸다</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>화물의 양·크기·무게와 배송 지역에 맞는 차종과 대수를 배정한다</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>배송 시간 약속보다 운전자의 선호를 우선한다</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>차량 수를 줄이기 위해 최대적재량을 넘겨 싣는다</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>배차는 화물 특성과 배송 조건에 맞는 차를 골라 적재 효율과 서비스를 함께 높이는 것이 원칙이다.</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>화물에 차를 맞추는 것이지, 차에 화물을 억지로 맞추는 것이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="N201" s="3" t="n"/>
-      <c r="O201" s="3" t="n"/>
-      <c r="P201" s="3" t="n"/>
-      <c r="Q201" s="3" t="n"/>
+      <c r="O201" s="3" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q201" s="3" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SERVICE-0201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>여러 곳을 배송할 때 경로를 짜는 방법으로 가장 바람직한 것은?</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>같은 방향·가까운 지역끼리 묶어 겹치거나 되돌아가는 거리를 줄인다</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>주문이 들어온 순서대로만 지역과 관계없이 배송한다</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>도로 상황은 고려하지 않고 지도상 직선거리만 본다</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>매일 경로를 바꾸어 운전자가 지루하지 않게 한다</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>배송 지역을 묶고 순서를 정해 중복·역주행 거리를 줄이면 시간과 연료비를 아낄 수 있다.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>지도 위에 그린 선이 꼬이지 않아야 합니다.</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M202" t="n">
+        <v>2</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SERVICE-0202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>작은 물류 거점 여러 곳을 줄이고 대형 거점으로 통합할 때 기대할 수 있는 효과로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>모든 고객까지의 배송 거리가 반드시 짧아진다</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>재고 보유량이 늘어난다</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>거점 간 수송이 필요 없어진다</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>재고와 관리비를 줄이고 거점 간 대량 수송으로 수송비를 낮출 수 있다</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>4</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>거점을 집약하면 재고·시설 관리비가 줄고 대량 수송의 이점이 생기지만, 일부 고객까지의 배송 거리는 늘어날 수 있다.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>재고를 한곳에 모으면 무엇이 줄어드는지 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M203" t="n">
+        <v>3</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SERVICE-0203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>공급망 리스크의 예로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>자연재해로 부품 공장의 가동이 멈춘다</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>거래처와 정기적으로 회의를 열어 정보를 나눈다</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>항만 파업으로 수출입 화물이 지연된다</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>핵심 공급업체가 부도를 낸다</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>공급망 리스크는 공급·생산·운송이 끊기거나 지연될 위험을 말하며, 정보 공유 회의는 오히려 위험을 줄이는 활동이다.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>위험 요인과 위험을 줄이는 활동을 구분하세요.</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SERVICE-0204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>한 공급업체에만 의존하다가 공급이 끊기는 위험을 줄이는 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>한 업체에 주문을 더 몰아준다</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>공급처를 여러 곳으로 다변화한다</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>재고를 전혀 두지 않는다</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>공급업체와 정보를 공유하지 않는다</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>2</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>공급처를 여러 곳 확보하면 한 곳에 문제가 생겨도 다른 곳에서 공급받을 수 있다.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>'달걀을 한 바구니에 담지 말라'는 말을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M205" t="n">
+        <v>2</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SERVICE-0205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>수요 변동이나 공급 지연에 대비해 평소 필요한 양보다 추가로 보유하는 재고는?</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>안전재고</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>불용재고</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>운송 중 재고</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>투기재고</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>안전재고는 예상치 못한 수요 증가나 납기 지연으로 품절이 나는 것을 막기 위한 여유 재고이다.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>만일을 대비한 '완충' 역할을 하는 재고입니다.</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M206" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SERVICE-0206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>공급망 전체에서 물품의 위치·재고·이동 상태를 실시간으로 파악할 수 있는 정도를 뜻하는 말은?</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>채찍 효과</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>리드타임</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>상충관계</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>공급망 가시성</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>4</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>공급망 가시성은 공급망의 흐름을 얼마나 잘 '볼 수 있는가'를 뜻하며, 위험 대응과 재고 관리의 기반이 된다.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>공급망 어디에 무엇이 얼마나 있는지 한눈에 파악되는 상태를 가리킵니다.</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M207" t="n">
+        <v>3</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SERVICE-0207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>그린 물류의 실천 방법으로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>포장 상자를 크게 만들고 완충재를 넉넉히 넣는다</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>전기·수소 화물차를 도입한다</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>재사용할 수 있는 운송 용기를 쓴다</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>공동배송으로 운행 횟수를 줄인다</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>과대 포장은 자원 낭비와 적재 효율 저하를 가져오므로 그린 물류와 반대된다.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>쓰레기와 빈 공간이 늘어나는 쪽을 찾으세요.</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M208" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SERVICE-0208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>순방향 물류와 비교한 역물류의 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>회수품의 품질이 모두 같아 분류가 필요 없다</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>회수되는 물량과 시점, 상태를 미리 예측하기 어렵다</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>발생 시점이 정확히 정해져 있다</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>처리 비용이 거의 들지 않는다</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>역물류는 반품·회수가 언제, 얼마나, 어떤 상태로 들어올지 불확실해 계획과 분류가 어렵다.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>되돌아오는 물건은 언제 올지 알 수 있을까요?</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M209" t="n">
+        <v>3</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SERVICE-0209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>화물정보망(화물 운송 정보 플랫폼)을 이용할 때의 효과로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>운송 계약 없이도 운임을 받을 수 있게 한다</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>차량 정비 주기를 자동으로 늘려 준다</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>화주의 운송 요청과 빈 차 정보를 빠르게 연결해 공차 운행을 줄인다</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>운전자의 휴게시간을 줄여 준다</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>3</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>화물정보망은 화물과 차량 정보를 실시간으로 이어 주어 빈 차 대기·운행을 줄이고 배차를 빠르게 한다.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>화물을 찾는 차와 차를 찾는 화물을 이어 주는 역할입니다.</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M210" t="n">
+        <v>2</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SERVICE-0210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EDI를 도입했을 때 기대되는 효과로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>서류 처리 시간이 줄어든다</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>종이 서류 사용량과 우편 비용이 늘어난다</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>수작업 입력 오류가 줄어든다</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>거래 정보를 빠르게 주고받을 수 있다</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>EDI는 종이 문서를 전자 문서로 바꾸는 것이므로 서류·우편 비용은 오히려 줄어든다.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>종이 대신 무엇을 주고받는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M211" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SERVICE-0211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>배송을 마친 순간 수하인의 서명이나 사진을 단말기로 받아 배송 완료를 증명하는 것은?</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>POD</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>CVO</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>POD는 배송 완료를 증빙하는 자료로, 전자 단말기의 서명·사진으로 받아 분쟁을 예방한다.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>POS는 판매 시점, EDI는 전자문서 교환에 관한 약어라는 점과 구분해 보세요.</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SERVICE-0212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>냉장 화물을 운송할 때 적재함 온도를 실시간으로 기록·전송하는 장치를 쓰는 주된 목적은?</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>화물의 무게를 자동으로 재기 위해</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>운전자의 운전 시간을 줄이기 위해</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>통행료를 자동으로 내기 위해</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>운송 중 온도 이탈을 바로 알아차리고 품질 관리 상태를 증명하기 위해</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>4</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>온도 기록 장치는 이탈 시 즉시 조치하게 해 주고, 운송 중 온도가 지켜졌음을 화주에게 증명하는 자료가 된다.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>출발 전 한 번 확인하는 것과 운송 내내 남기는 기록의 차이를 생각하세요.</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SERVICE-0213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>해상 운송의 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>운송 속도가 가장 빠르다</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>기상의 영향을 거의 받지 않는다</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>고객의 문 앞까지 바로 배송할 수 있다</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>대량 화물을 낮은 운임으로 멀리 나를 수 있지만 운송 시간이 길다</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>4</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>해상 운송은 대량·장거리·저운임이 장점이지만 속도가 느리고 기상 영향을 받는다.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>큰 배가 바다를 건너는 모습을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M214" t="n">
+        <v>2</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SERVICE-0214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>항공 운송에 가장 알맞은 화물은?</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>시멘트·모래 같은 건설 자재</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>석탄·철광석 같은 원자재</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>원유 같은 대량 액체 화물</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>부피가 작고 값이 비싸며 빨리 보내야 하는 반도체·의약품</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>4</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>항공 운송은 운임이 비싸지만 빠르므로 가볍고 고가이며 긴급한 화물에 알맞다.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>비싼 운임을 내도 아깝지 않은 화물을 찾으세요.</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SERVICE-0215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>철도 운송의 단점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>대량 화물 운송에 불리하다</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>날씨의 영향을 크게 받는다</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>역과 역 사이만 운송하므로 문전 운송을 위해 화물차 연계가 필요하다</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>장거리 운송비가 도로보다 비싸다</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>3</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>철도는 대량·장거리에 유리하지만 선로가 있는 곳만 다닐 수 있어 출발·도착지에서 화물차 환적이 필요하다.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>기차가 갈 수 있는 곳에는 한계가 있습니다.</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M216" t="n">
+        <v>2</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SERVICE-0216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>도로(화물자동차) 운송의 단점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>문전 운송이 어렵다</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>소량 화물을 다루기 어렵다</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>대량 화물을 장거리로 나를 때 단위당 운송비가 높고 에너지·환경 부담이 크다</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>운송 일정을 바꾸기 어렵다</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>3</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>화물자동차는 기동성이 좋지만 한 번에 실을 수 있는 양이 적어 대량·장거리에서는 비용과 배출가스 부담이 크다.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>화물차의 장점이 무엇인지 먼저 떠올리고 그 반대쪽을 보세요.</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M217" t="n">
+        <v>3</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SERVICE-0217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>원유·가스처럼 액체·기체 화물을 연속으로 보내며, 한 번 설치하면 운영비가 적게 드는 운송 수단은?</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>항공 운송</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>연안해운</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>파이프라인 운송</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>철도 컨테이너 운송</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>3</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>파이프라인은 초기 건설비가 크지만 유지·운영비가 낮고 연속 수송이 가능하며, 운송할 수 있는 화물 종류가 제한된다.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>수도관으로 물이 흐르는 원리와 같습니다.</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M218" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SERVICE-0218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>일반적으로 단거리 운송에서 비용 면에서 가장 유리한 운송 수단은?</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>화물자동차</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>해상 운송</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>항공 운송</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>철도 운송</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>단거리는 상·하역과 환적 비용이 적은 화물자동차가 유리하고, 거리가 길어질수록 철도·해상이 유리해진다.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>짧은 거리에서는 싣고 내리는 횟수가 비용을 좌우합니다.</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M219" t="n">
+        <v>3</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SERVICE-0219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>화물자동차 운송이 다양한 화물에 대응할 수 있는 이유로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>모든 화물을 한 가지 차종으로만 운송한다</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>운송 경로가 선로로 정해져 있다</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>항만에서만 화물을 싣고 내린다</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>냉동·탱크·덤프 등 화물 특성에 맞는 다양한 차종이 있다</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>4</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>화물자동차는 화물 성질에 맞춘 특수 차종이 다양해 여러 화주의 요구에 유연하게 대응할 수 있다.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>냉동식품, 기름, 모래를 나르는 차의 모양을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SERVICE-0220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>화물 운송 수요는 그 자체가 목적이 아니라 생산·소비 활동에 따라 생겨난다는 뜻의 말은?</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>본원적 수요</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>잠재 수요</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>대체 수요</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>파생수요</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>4</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>운송은 물건을 생산하고 소비하는 활동 때문에 필요해지는 파생수요이므로 경기와 산업 활동에 따라 변한다.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>사람들이 운송 자체를 원해서가 아니라 물건을 만들고 쓰기 때문에 운송이 필요해집니다.</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M221" t="n">
+        <v>3</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통경제학 일반 이론(운송 수요의 파생성), 교재 직접 수록 여부 미확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SERVICE-0221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>명절 전처럼 택배 물량이 갑자기 몰리는 시기에 대한 대응으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>임시 인력과 차량을 미리 확보하고 고객에게 지연 가능성을 미리 안내한다</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>평소 인력만으로 처리하고 지연은 알리지 않는다</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>물량이 많으니 운전자의 휴게시간을 없앤다</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>최대적재량을 넘겨 실어 운행 횟수를 줄인다</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>성수기에는 수요 변동에 대비해 자원을 미리 확보하고 고객에게 정보를 제공해 불만을 줄인다.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>미리 준비하고 미리 알리는 것이 핵심입니다.</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M222" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류관리 일반 이론(물류관리사 교재 수준), 원문 미대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SERVICE-0222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>고객에게 명함을 건넬 때의 예절로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>일어선 자세에서 상대가 글자를 바로 읽을 수 있는 방향으로 두 손으로 건넨다</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>앉은 채로 한 손으로 테이블 위에 밀어 건넨다</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>바지 뒷주머니의 지갑에서 꺼내 건넨다</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>받은 명함은 보지 않고 바로 주머니에 넣는다</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>명함은 일어서서 상대가 읽기 쉬운 방향으로 두 손으로 건네는 것이 기본이다. 받은 명함은 잠시 읽어 이름과 소속을 확인한 뒤 소중히 보관한다.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>명함은 그 사람의 얼굴과 같다는 말이 있습니다.</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M223" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 고객 응대 예절 일반 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SERVICE-0223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>물류센터 선반(랙)에 붙은 표시기에 불이 켜지고 꺼낼 수량이 숫자로 표시되어, 작업자가 그 안내에 따라 보관 장소에서 물품을 꺼내도록 돕는 시스템은?</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>DAS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>DPS</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>3</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>DPS(Digital Picking System)는 표시기의 불빛과 숫자로 꺼낼 위치와 수량을 알려 피킹 오류와 시간을 줄인다. DAS는 꺼낸 물품을 배송처별로 나누는 분배 작업을 돕는 시스템이다.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>이 시스템이 돕는 작업은 배송처별 '분배'가 아니라 보관 장소에서 '꺼내는' 일입니다.</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M224" t="n">
+        <v>3</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류 정보화 일반 내용(DPS·DAS 구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SERVICE-0224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>온라인 판매자를 대신해 상품 보관부터 주문에 따른 피킹·포장·배송, 교환·반품 처리까지 한꺼번에 맡아 주는 물류 서비스는?</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>풀필먼트 서비스</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>크로스도킹</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>밀크런</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>모달 시프트</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>풀필먼트는 주문 이행에 필요한 보관·피킹·포장·출고·배송·반품 처리를 일괄 대행하는 서비스다. 크로스도킹은 입고 화물을 보관하지 않고 바로 출고하는 방식, 밀크런은 한 차량이 여러 곳을 순회 집하하는 방식이다.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>판매자는 상품을 파는 일에 집중하고, 그 뒤의 물류 과정 전체를 한 업체가 대신 맡는 방식입니다.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M225" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류 일반 내용(전자상거래 물류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SERVICE-0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>일정 기간의 출고량(또는 매출액)을 같은 기간의 평균 재고량(액)으로 나눈 값으로, 재고가 얼마나 빨리 팔려 나가는지를 보여 주는 지표는?</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>안전재고율</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>재고회전율</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>적재율</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>공차율</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>재고회전율은 출고량(매출액)을 평균 재고로 나눈 값으로, 높을수록 재고가 빨리 소진되어 보관비와 재고 부담이 줄어든다. 적재율·공차율은 차량 운행 효율 지표다.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>창고에 들어온 재고가 기간 동안 몇 차례나 나가고 다시 채워졌는지를 나타냅니다.</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M226" t="n">
+        <v>2</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 물류 일반 내용(재고관리 지표)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="4">
